--- a/thaco/color/1_Office_color Mid Cycle.xlsx
+++ b/thaco/color/1_Office_color Mid Cycle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1630A578-CCD7-F643-8005-875694D5ECDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8508E364-75E8-B94D-BB23-30761D63FF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38440" yWindow="500" windowWidth="38360" windowHeight="20700" tabRatio="761" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38480" yWindow="500" windowWidth="38360" windowHeight="20700" tabRatio="761" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="1" r:id="rId1"/>
@@ -493,7 +493,7 @@
     <definedName name="_ELF2" hidden="1">{"'Sheet1'!$L$16"}</definedName>
     <definedName name="_Fill" hidden="1">#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bảng lương CB-NV'!$A$12:$CI$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Bảng lương tạm ứng kỳ 1'!$A$12:$CI$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Bảng lương tạm ứng kỳ 1'!$A$12:$CG$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mô tả Bảng lương CB-NV'!$A$9:$CI$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Mô tả Bảng lương tạm ứng kỳ 1'!$A$9:$CI$14</definedName>
     <definedName name="_G1">{"th152.xls"}</definedName>
@@ -2702,7 +2702,7 @@
     <definedName name="PRICE">#REF!</definedName>
     <definedName name="PRICE1">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Bảng lương CB-NV'!$A$1:$BU$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Bảng lương tạm ứng kỳ 1'!$A$1:$BU$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Bảng lương tạm ứng kỳ 1'!$A$1:$BT$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Mô tả Bảng lương CB-NV'!$A$1:$BU$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Mô tả Bảng lương tạm ứng kỳ 1'!$A$1:$BU$14</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
@@ -4545,7 +4545,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="162">
   <si>
     <t>COMPANY …..............</t>
   </si>
@@ -5822,7 +5822,7 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="505">
+  <cellXfs count="496">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6744,12 +6744,6 @@
     <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -6804,9 +6798,6 @@
     </xf>
     <xf numFmtId="164" fontId="63" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6838,18 +6829,11 @@
     <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -6883,9 +6867,6 @@
     <xf numFmtId="164" fontId="26" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6899,9 +6880,6 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="167" fontId="15" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6927,9 +6905,6 @@
     <xf numFmtId="165" fontId="57" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="57" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -14894,206 +14869,200 @@
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:CI26"/>
+  <dimension ref="A1:CG26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="5.5" style="439" customWidth="1"/>
-    <col min="2" max="2" width="8.5" style="440" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="441" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5" style="362" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="5.5" style="362" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="5.5" style="363" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="13.6640625" style="365" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="365" customWidth="1"/>
-    <col min="9" max="9" width="12.5" style="444" customWidth="1"/>
-    <col min="10" max="10" width="7.5" style="444" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="24" width="7.1640625" style="364" customWidth="1"/>
-    <col min="25" max="47" width="12.33203125" style="365" customWidth="1"/>
-    <col min="48" max="49" width="13" style="365" customWidth="1"/>
-    <col min="50" max="50" width="6.6640625" style="365" customWidth="1"/>
-    <col min="51" max="53" width="10.5" style="365" customWidth="1" outlineLevel="1"/>
-    <col min="54" max="71" width="10.5" style="365" customWidth="1"/>
-    <col min="72" max="72" width="12.5" style="365" customWidth="1"/>
-    <col min="73" max="73" width="12.5" style="365" hidden="1" customWidth="1"/>
-    <col min="74" max="74" width="12.5" style="365" customWidth="1"/>
-    <col min="75" max="79" width="12.6640625" style="365" customWidth="1" outlineLevel="1"/>
-    <col min="80" max="80" width="12.6640625" style="445" customWidth="1" outlineLevel="1"/>
-    <col min="81" max="82" width="10.6640625" style="445" customWidth="1" outlineLevel="1"/>
-    <col min="83" max="83" width="19.5" style="446" customWidth="1"/>
-    <col min="84" max="84" width="12.33203125" style="446" customWidth="1"/>
-    <col min="85" max="85" width="12.5" style="446" customWidth="1"/>
-    <col min="86" max="86" width="11.6640625" style="446" customWidth="1"/>
-    <col min="87" max="87" width="9.1640625" style="446" customWidth="1"/>
-    <col min="88" max="16384" width="9.1640625" style="446"/>
+    <col min="1" max="1" width="5.5" style="430" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="431" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="432" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5" style="360" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="5.5" style="360" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="5.5" style="361" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="13.6640625" style="363" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="363" customWidth="1"/>
+    <col min="9" max="9" width="12.5" style="435" customWidth="1"/>
+    <col min="10" max="10" width="7.5" style="435" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="24" width="7.1640625" style="362" customWidth="1"/>
+    <col min="25" max="47" width="12.33203125" style="363" customWidth="1"/>
+    <col min="48" max="49" width="13" style="363" customWidth="1"/>
+    <col min="50" max="50" width="6.6640625" style="363" customWidth="1"/>
+    <col min="51" max="53" width="10.5" style="363" customWidth="1" outlineLevel="1"/>
+    <col min="54" max="71" width="10.5" style="363" customWidth="1"/>
+    <col min="72" max="72" width="12.5" style="363" customWidth="1"/>
+    <col min="73" max="77" width="12.6640625" style="363" customWidth="1" outlineLevel="1"/>
+    <col min="78" max="78" width="12.6640625" style="436" customWidth="1" outlineLevel="1"/>
+    <col min="79" max="80" width="10.6640625" style="436" customWidth="1" outlineLevel="1"/>
+    <col min="81" max="81" width="19.5" style="437" customWidth="1"/>
+    <col min="82" max="82" width="12.33203125" style="437" customWidth="1"/>
+    <col min="83" max="83" width="12.5" style="437" customWidth="1"/>
+    <col min="84" max="84" width="11.6640625" style="437" customWidth="1"/>
+    <col min="85" max="85" width="9.1640625" style="437" customWidth="1"/>
+    <col min="86" max="16384" width="9.1640625" style="437"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:87" s="343" customFormat="1" ht="23.25" customHeight="1" outlineLevel="1">
-      <c r="A1" s="366" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="367"/>
-      <c r="C1" s="368"/>
-      <c r="D1" s="369"/>
-      <c r="E1" s="369"/>
-      <c r="F1" s="369"/>
-      <c r="I1" s="400"/>
-      <c r="K1" s="370"/>
-      <c r="L1" s="370"/>
-      <c r="M1" s="370"/>
-      <c r="N1" s="370"/>
-      <c r="O1" s="370"/>
-      <c r="P1" s="370"/>
-      <c r="Q1" s="370"/>
-      <c r="R1" s="370"/>
-      <c r="S1" s="370"/>
-      <c r="T1" s="370"/>
-      <c r="U1" s="370"/>
-      <c r="V1" s="370"/>
-      <c r="W1" s="370"/>
-      <c r="X1" s="370"/>
-      <c r="Y1" s="371"/>
-      <c r="Z1" s="371"/>
-      <c r="AA1" s="371"/>
-      <c r="AB1" s="371"/>
-      <c r="AC1" s="371"/>
-      <c r="AD1" s="371"/>
-      <c r="AE1" s="371"/>
-      <c r="AF1" s="371"/>
-      <c r="AG1" s="371"/>
-      <c r="AH1" s="371"/>
-      <c r="AI1" s="371"/>
-      <c r="AJ1" s="371"/>
-      <c r="AK1" s="371"/>
-      <c r="AL1" s="371"/>
-      <c r="AM1" s="371"/>
-      <c r="AN1" s="371"/>
-      <c r="AO1" s="371"/>
-      <c r="AP1" s="371"/>
-      <c r="AQ1" s="371"/>
-      <c r="AR1" s="371"/>
-      <c r="AS1" s="371"/>
-      <c r="AT1" s="371"/>
-      <c r="AU1" s="371"/>
-      <c r="AV1" s="371"/>
-      <c r="AW1" s="371"/>
-      <c r="AX1" s="371"/>
-      <c r="AY1" s="371"/>
-      <c r="AZ1" s="371"/>
-      <c r="BA1" s="371"/>
-      <c r="BB1" s="371"/>
-      <c r="BC1" s="371"/>
-      <c r="BD1" s="371"/>
-      <c r="BE1" s="371"/>
-      <c r="BF1" s="371"/>
-      <c r="BG1" s="371"/>
-      <c r="BH1" s="371"/>
-      <c r="BI1" s="371"/>
-      <c r="BJ1" s="371"/>
-      <c r="BK1" s="371"/>
-      <c r="BL1" s="371"/>
-      <c r="BM1" s="371"/>
-      <c r="BN1" s="372"/>
-      <c r="BO1" s="372"/>
-      <c r="BP1" s="371"/>
-      <c r="BQ1" s="371"/>
-      <c r="BR1" s="371"/>
-      <c r="BS1" s="371"/>
+    <row r="1" spans="1:85" s="343" customFormat="1" ht="23.25" customHeight="1" outlineLevel="1">
+      <c r="A1" s="364" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="365"/>
+      <c r="C1" s="366"/>
+      <c r="D1" s="367"/>
+      <c r="E1" s="367"/>
+      <c r="F1" s="367"/>
+      <c r="I1" s="394"/>
+      <c r="K1" s="368"/>
+      <c r="L1" s="368"/>
+      <c r="M1" s="368"/>
+      <c r="N1" s="368"/>
+      <c r="O1" s="368"/>
+      <c r="P1" s="368"/>
+      <c r="Q1" s="368"/>
+      <c r="R1" s="368"/>
+      <c r="S1" s="368"/>
+      <c r="T1" s="368"/>
+      <c r="U1" s="368"/>
+      <c r="V1" s="368"/>
+      <c r="W1" s="368"/>
+      <c r="X1" s="368"/>
+      <c r="Y1" s="369"/>
+      <c r="Z1" s="369"/>
+      <c r="AA1" s="369"/>
+      <c r="AB1" s="369"/>
+      <c r="AC1" s="369"/>
+      <c r="AD1" s="369"/>
+      <c r="AE1" s="369"/>
+      <c r="AF1" s="369"/>
+      <c r="AG1" s="369"/>
+      <c r="AH1" s="369"/>
+      <c r="AI1" s="369"/>
+      <c r="AJ1" s="369"/>
+      <c r="AK1" s="369"/>
+      <c r="AL1" s="369"/>
+      <c r="AM1" s="369"/>
+      <c r="AN1" s="369"/>
+      <c r="AO1" s="369"/>
+      <c r="AP1" s="369"/>
+      <c r="AQ1" s="369"/>
+      <c r="AR1" s="369"/>
+      <c r="AS1" s="369"/>
+      <c r="AT1" s="369"/>
+      <c r="AU1" s="369"/>
+      <c r="AV1" s="369"/>
+      <c r="AW1" s="369"/>
+      <c r="AX1" s="369"/>
+      <c r="AY1" s="369"/>
+      <c r="AZ1" s="369"/>
+      <c r="BA1" s="369"/>
+      <c r="BB1" s="369"/>
+      <c r="BC1" s="369"/>
+      <c r="BD1" s="369"/>
+      <c r="BE1" s="369"/>
+      <c r="BF1" s="369"/>
+      <c r="BG1" s="369"/>
+      <c r="BH1" s="369"/>
+      <c r="BI1" s="369"/>
+      <c r="BJ1" s="369"/>
+      <c r="BK1" s="369"/>
+      <c r="BL1" s="369"/>
+      <c r="BM1" s="369"/>
+      <c r="BN1" s="370"/>
+      <c r="BO1" s="370"/>
+      <c r="BP1" s="369"/>
+      <c r="BQ1" s="369"/>
+      <c r="BR1" s="369"/>
+      <c r="BS1" s="369"/>
       <c r="BU1" s="371"/>
       <c r="BV1" s="371"/>
-      <c r="BW1" s="373"/>
-      <c r="BX1" s="373"/>
-      <c r="BY1" s="373"/>
-      <c r="BZ1" s="373"/>
-      <c r="CA1" s="373"/>
-      <c r="CB1" s="374"/>
-      <c r="CC1" s="374"/>
-      <c r="CD1" s="374"/>
+      <c r="BW1" s="371"/>
+      <c r="BX1" s="371"/>
+      <c r="BY1" s="371"/>
+      <c r="BZ1" s="372"/>
+      <c r="CA1" s="372"/>
+      <c r="CB1" s="372"/>
     </row>
-    <row r="2" spans="1:87" s="343" customFormat="1" ht="19.25" customHeight="1" outlineLevel="1">
-      <c r="A2" s="375" t="s">
+    <row r="2" spans="1:85" s="343" customFormat="1" ht="19.25" customHeight="1" outlineLevel="1">
+      <c r="A2" s="373" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="367"/>
-      <c r="C2" s="376"/>
-      <c r="D2" s="369"/>
-      <c r="E2" s="369"/>
-      <c r="F2" s="369"/>
-      <c r="I2" s="400"/>
-      <c r="K2" s="370"/>
-      <c r="L2" s="370"/>
-      <c r="M2" s="370"/>
-      <c r="N2" s="370"/>
-      <c r="O2" s="370"/>
-      <c r="P2" s="370"/>
-      <c r="Q2" s="370"/>
-      <c r="R2" s="370"/>
-      <c r="S2" s="370"/>
-      <c r="T2" s="370"/>
-      <c r="U2" s="370"/>
-      <c r="V2" s="370"/>
-      <c r="W2" s="370"/>
-      <c r="X2" s="370"/>
-      <c r="Y2" s="371"/>
-      <c r="Z2" s="371"/>
-      <c r="AA2" s="371"/>
-      <c r="AB2" s="371"/>
-      <c r="AC2" s="371"/>
-      <c r="AD2" s="371"/>
-      <c r="AE2" s="371"/>
-      <c r="AF2" s="371"/>
-      <c r="AG2" s="371"/>
-      <c r="AH2" s="371"/>
-      <c r="AI2" s="371"/>
-      <c r="AJ2" s="371"/>
-      <c r="AK2" s="371"/>
-      <c r="AL2" s="371"/>
-      <c r="AM2" s="371"/>
-      <c r="AN2" s="371"/>
-      <c r="AO2" s="371"/>
-      <c r="AP2" s="371"/>
-      <c r="AQ2" s="371"/>
-      <c r="AR2" s="371"/>
-      <c r="AS2" s="371"/>
-      <c r="AT2" s="371"/>
-      <c r="AU2" s="371"/>
-      <c r="AV2" s="371"/>
-      <c r="AW2" s="371"/>
-      <c r="AX2" s="371"/>
-      <c r="AY2" s="371"/>
-      <c r="AZ2" s="371"/>
-      <c r="BA2" s="371"/>
-      <c r="BB2" s="371"/>
-      <c r="BC2" s="371"/>
-      <c r="BD2" s="371"/>
-      <c r="BE2" s="371"/>
-      <c r="BF2" s="371"/>
-      <c r="BG2" s="371"/>
-      <c r="BH2" s="371"/>
-      <c r="BI2" s="371"/>
-      <c r="BJ2" s="371"/>
-      <c r="BK2" s="371"/>
-      <c r="BL2" s="371"/>
-      <c r="BM2" s="371"/>
-      <c r="BN2" s="371"/>
-      <c r="BO2" s="371"/>
-      <c r="BP2" s="371"/>
-      <c r="BQ2" s="371"/>
-      <c r="BR2" s="371"/>
-      <c r="BS2" s="371"/>
-      <c r="BT2" s="371"/>
-      <c r="BU2" s="371"/>
-      <c r="BV2" s="371"/>
-      <c r="BW2" s="377"/>
-      <c r="BX2" s="377"/>
-      <c r="BY2" s="377"/>
-      <c r="BZ2" s="377"/>
-      <c r="CA2" s="377"/>
-      <c r="CB2" s="376"/>
-      <c r="CC2" s="376"/>
-      <c r="CD2" s="376"/>
+      <c r="B2" s="365"/>
+      <c r="C2" s="374"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="I2" s="394"/>
+      <c r="K2" s="368"/>
+      <c r="L2" s="368"/>
+      <c r="M2" s="368"/>
+      <c r="N2" s="368"/>
+      <c r="O2" s="368"/>
+      <c r="P2" s="368"/>
+      <c r="Q2" s="368"/>
+      <c r="R2" s="368"/>
+      <c r="S2" s="368"/>
+      <c r="T2" s="368"/>
+      <c r="U2" s="368"/>
+      <c r="V2" s="368"/>
+      <c r="W2" s="368"/>
+      <c r="X2" s="368"/>
+      <c r="Y2" s="369"/>
+      <c r="Z2" s="369"/>
+      <c r="AA2" s="369"/>
+      <c r="AB2" s="369"/>
+      <c r="AC2" s="369"/>
+      <c r="AD2" s="369"/>
+      <c r="AE2" s="369"/>
+      <c r="AF2" s="369"/>
+      <c r="AG2" s="369"/>
+      <c r="AH2" s="369"/>
+      <c r="AI2" s="369"/>
+      <c r="AJ2" s="369"/>
+      <c r="AK2" s="369"/>
+      <c r="AL2" s="369"/>
+      <c r="AM2" s="369"/>
+      <c r="AN2" s="369"/>
+      <c r="AO2" s="369"/>
+      <c r="AP2" s="369"/>
+      <c r="AQ2" s="369"/>
+      <c r="AR2" s="369"/>
+      <c r="AS2" s="369"/>
+      <c r="AT2" s="369"/>
+      <c r="AU2" s="369"/>
+      <c r="AV2" s="369"/>
+      <c r="AW2" s="369"/>
+      <c r="AX2" s="369"/>
+      <c r="AY2" s="369"/>
+      <c r="AZ2" s="369"/>
+      <c r="BA2" s="369"/>
+      <c r="BB2" s="369"/>
+      <c r="BC2" s="369"/>
+      <c r="BD2" s="369"/>
+      <c r="BE2" s="369"/>
+      <c r="BF2" s="369"/>
+      <c r="BG2" s="369"/>
+      <c r="BH2" s="369"/>
+      <c r="BI2" s="369"/>
+      <c r="BJ2" s="369"/>
+      <c r="BK2" s="369"/>
+      <c r="BL2" s="369"/>
+      <c r="BM2" s="369"/>
+      <c r="BN2" s="369"/>
+      <c r="BO2" s="369"/>
+      <c r="BP2" s="369"/>
+      <c r="BQ2" s="369"/>
+      <c r="BR2" s="369"/>
+      <c r="BS2" s="369"/>
+      <c r="BT2" s="369"/>
+      <c r="BU2" s="375"/>
+      <c r="BV2" s="375"/>
+      <c r="BW2" s="375"/>
+      <c r="BX2" s="375"/>
+      <c r="BY2" s="375"/>
+      <c r="BZ2" s="374"/>
+      <c r="CA2" s="374"/>
+      <c r="CB2" s="374"/>
     </row>
-    <row r="3" spans="1:87" s="345" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="378"/>
+    <row r="3" spans="1:85" s="345" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
+      <c r="A3" s="376"/>
       <c r="B3" s="344"/>
       <c r="C3" s="344"/>
       <c r="D3" s="344"/>
@@ -15165,417 +15134,407 @@
       <c r="BR3" s="344"/>
       <c r="BS3" s="344"/>
       <c r="BT3" s="344"/>
-      <c r="BU3" s="344"/>
-      <c r="BV3" s="379"/>
-      <c r="BW3" s="380" t="s">
+      <c r="BU3" s="377" t="s">
         <v>2</v>
       </c>
+      <c r="BV3" s="344"/>
+      <c r="BW3" s="344"/>
       <c r="BX3" s="344"/>
       <c r="BY3" s="344"/>
       <c r="BZ3" s="344"/>
-      <c r="CA3" s="344"/>
-      <c r="CB3" s="344"/>
-      <c r="CC3" s="381"/>
-      <c r="CD3" s="381"/>
+      <c r="CA3" s="378"/>
+      <c r="CB3" s="378"/>
     </row>
-    <row r="4" spans="1:87" s="345" customFormat="1" ht="21.5" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A4" s="382"/>
-      <c r="B4" s="382"/>
-      <c r="C4" s="382"/>
-      <c r="D4" s="382"/>
-      <c r="E4" s="382"/>
-      <c r="F4" s="382"/>
-      <c r="G4" s="382"/>
-      <c r="H4" s="382"/>
-      <c r="I4" s="400"/>
-      <c r="K4" s="382"/>
-      <c r="L4" s="382"/>
-      <c r="M4" s="382"/>
-      <c r="N4" s="382"/>
-      <c r="O4" s="382"/>
-      <c r="P4" s="382"/>
-      <c r="Q4" s="382"/>
-      <c r="R4" s="382"/>
-      <c r="S4" s="382"/>
-      <c r="T4" s="382"/>
-      <c r="U4" s="382"/>
-      <c r="V4" s="383"/>
-      <c r="W4" s="383"/>
-      <c r="X4" s="383"/>
-      <c r="Y4" s="383"/>
-      <c r="Z4" s="383"/>
-      <c r="AA4" s="383"/>
-      <c r="AB4" s="383"/>
-      <c r="AC4" s="383"/>
-      <c r="AD4" s="383"/>
-      <c r="AE4" s="383"/>
-      <c r="AF4" s="383"/>
-      <c r="AG4" s="383"/>
-      <c r="AH4" s="383"/>
-      <c r="AI4" s="383"/>
-      <c r="AJ4" s="383"/>
-      <c r="AK4" s="383"/>
-      <c r="AL4" s="383"/>
-      <c r="AM4" s="382"/>
-      <c r="AN4" s="382"/>
-      <c r="AO4" s="382"/>
-      <c r="AP4" s="382"/>
-      <c r="AQ4" s="382"/>
-      <c r="AR4" s="382"/>
-      <c r="AS4" s="382"/>
-      <c r="AT4" s="382"/>
-      <c r="AU4" s="382"/>
-      <c r="AV4" s="382"/>
-      <c r="AW4" s="382"/>
-      <c r="AX4" s="382"/>
-      <c r="AY4" s="382"/>
-      <c r="AZ4" s="382"/>
-      <c r="BA4" s="382"/>
-      <c r="BB4" s="382"/>
-      <c r="BC4" s="382"/>
-      <c r="BD4" s="382"/>
-      <c r="BE4" s="382"/>
-      <c r="BF4" s="382"/>
-      <c r="BG4" s="382"/>
-      <c r="BH4" s="382"/>
-      <c r="BI4" s="382"/>
-      <c r="BJ4" s="382"/>
-      <c r="BK4" s="382"/>
-      <c r="BL4" s="382"/>
-      <c r="BM4" s="382"/>
-      <c r="BN4" s="382"/>
-      <c r="BO4" s="382"/>
-      <c r="BP4" s="382"/>
-      <c r="BQ4" s="382"/>
-      <c r="BR4" s="382"/>
-      <c r="BS4" s="382"/>
-      <c r="BT4" s="382"/>
-      <c r="BU4" s="382"/>
-      <c r="BV4" s="382"/>
+    <row r="4" spans="1:85" s="345" customFormat="1" ht="21.5" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A4" s="379"/>
+      <c r="B4" s="379"/>
+      <c r="C4" s="379"/>
+      <c r="D4" s="379"/>
+      <c r="E4" s="379"/>
+      <c r="F4" s="379"/>
+      <c r="G4" s="379"/>
+      <c r="H4" s="379"/>
+      <c r="I4" s="394"/>
+      <c r="K4" s="379"/>
+      <c r="L4" s="379"/>
+      <c r="M4" s="379"/>
+      <c r="N4" s="379"/>
+      <c r="O4" s="379"/>
+      <c r="P4" s="379"/>
+      <c r="Q4" s="379"/>
+      <c r="R4" s="379"/>
+      <c r="S4" s="379"/>
+      <c r="T4" s="379"/>
+      <c r="U4" s="379"/>
+      <c r="V4" s="380"/>
+      <c r="W4" s="380"/>
+      <c r="X4" s="380"/>
+      <c r="Y4" s="380"/>
+      <c r="Z4" s="380"/>
+      <c r="AA4" s="380"/>
+      <c r="AB4" s="380"/>
+      <c r="AC4" s="380"/>
+      <c r="AD4" s="380"/>
+      <c r="AE4" s="380"/>
+      <c r="AF4" s="380"/>
+      <c r="AG4" s="380"/>
+      <c r="AH4" s="380"/>
+      <c r="AI4" s="380"/>
+      <c r="AJ4" s="380"/>
+      <c r="AK4" s="380"/>
+      <c r="AL4" s="380"/>
+      <c r="AM4" s="379"/>
+      <c r="AN4" s="379"/>
+      <c r="AO4" s="379"/>
+      <c r="AP4" s="379"/>
+      <c r="AQ4" s="379"/>
+      <c r="AR4" s="379"/>
+      <c r="AS4" s="379"/>
+      <c r="AT4" s="379"/>
+      <c r="AU4" s="379"/>
+      <c r="AV4" s="379"/>
+      <c r="AW4" s="379"/>
+      <c r="AX4" s="379"/>
+      <c r="AY4" s="379"/>
+      <c r="AZ4" s="379"/>
+      <c r="BA4" s="379"/>
+      <c r="BB4" s="379"/>
+      <c r="BC4" s="379"/>
+      <c r="BD4" s="379"/>
+      <c r="BE4" s="379"/>
+      <c r="BF4" s="379"/>
+      <c r="BG4" s="379"/>
+      <c r="BH4" s="379"/>
+      <c r="BI4" s="379"/>
+      <c r="BJ4" s="379"/>
+      <c r="BK4" s="379"/>
+      <c r="BL4" s="379"/>
+      <c r="BM4" s="379"/>
+      <c r="BN4" s="379"/>
+      <c r="BO4" s="379"/>
+      <c r="BP4" s="379"/>
+      <c r="BQ4" s="379"/>
+      <c r="BR4" s="379"/>
+      <c r="BS4" s="379"/>
+      <c r="BT4" s="379"/>
+      <c r="BU4" s="344"/>
+      <c r="BV4" s="344"/>
       <c r="BW4" s="344"/>
       <c r="BX4" s="344"/>
       <c r="BY4" s="344"/>
       <c r="BZ4" s="344"/>
-      <c r="CA4" s="344"/>
-      <c r="CB4" s="344"/>
-      <c r="CC4" s="381"/>
-      <c r="CD4" s="381"/>
+      <c r="CA4" s="378"/>
+      <c r="CB4" s="378"/>
     </row>
-    <row r="5" spans="1:87" s="345" customFormat="1" ht="20.25" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A5" s="382"/>
-      <c r="B5" s="382"/>
-      <c r="C5" s="382"/>
-      <c r="D5" s="382"/>
-      <c r="E5" s="382"/>
-      <c r="F5" s="382"/>
-      <c r="G5" s="382"/>
-      <c r="H5" s="382"/>
-      <c r="I5" s="400"/>
-      <c r="K5" s="382"/>
-      <c r="L5" s="382"/>
-      <c r="M5" s="382"/>
-      <c r="N5" s="382"/>
-      <c r="O5" s="382"/>
-      <c r="P5" s="382"/>
-      <c r="Q5" s="382"/>
-      <c r="R5" s="382"/>
-      <c r="S5" s="382"/>
-      <c r="T5" s="382"/>
-      <c r="U5" s="382"/>
-      <c r="V5" s="382"/>
-      <c r="W5" s="382"/>
-      <c r="X5" s="382"/>
-      <c r="Y5" s="382"/>
-      <c r="Z5" s="382"/>
-      <c r="AA5" s="382"/>
-      <c r="AB5" s="382"/>
-      <c r="AC5" s="382"/>
-      <c r="AD5" s="382"/>
-      <c r="AE5" s="382"/>
-      <c r="AF5" s="382"/>
-      <c r="AG5" s="382"/>
-      <c r="AH5" s="382"/>
-      <c r="AI5" s="382"/>
-      <c r="AJ5" s="382"/>
-      <c r="AK5" s="382"/>
-      <c r="AL5" s="382"/>
-      <c r="AM5" s="382"/>
-      <c r="AN5" s="382"/>
-      <c r="AO5" s="382"/>
-      <c r="AP5" s="382"/>
-      <c r="AQ5" s="382"/>
-      <c r="AR5" s="382"/>
-      <c r="AS5" s="382"/>
-      <c r="AT5" s="382"/>
-      <c r="AU5" s="382"/>
-      <c r="AV5" s="382"/>
-      <c r="AW5" s="382"/>
-      <c r="AX5" s="382"/>
-      <c r="AY5" s="382"/>
-      <c r="AZ5" s="382"/>
-      <c r="BA5" s="382"/>
-      <c r="BB5" s="382"/>
-      <c r="BC5" s="382"/>
-      <c r="BD5" s="382"/>
-      <c r="BE5" s="382"/>
-      <c r="BF5" s="382"/>
-      <c r="BG5" s="382"/>
-      <c r="BH5" s="382"/>
-      <c r="BI5" s="382"/>
-      <c r="BJ5" s="382"/>
-      <c r="BK5" s="382"/>
-      <c r="BL5" s="382"/>
-      <c r="BM5" s="382"/>
-      <c r="BN5" s="382"/>
-      <c r="BO5" s="382"/>
-      <c r="BP5" s="382"/>
-      <c r="BQ5" s="382"/>
-      <c r="BR5" s="382"/>
-      <c r="BS5" s="382"/>
-      <c r="BT5" s="382"/>
-      <c r="BU5" s="382"/>
-      <c r="BV5" s="382"/>
+    <row r="5" spans="1:85" s="345" customFormat="1" ht="20.25" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A5" s="379"/>
+      <c r="B5" s="379"/>
+      <c r="C5" s="379"/>
+      <c r="D5" s="379"/>
+      <c r="E5" s="379"/>
+      <c r="F5" s="379"/>
+      <c r="G5" s="379"/>
+      <c r="H5" s="379"/>
+      <c r="I5" s="394"/>
+      <c r="K5" s="379"/>
+      <c r="L5" s="379"/>
+      <c r="M5" s="379"/>
+      <c r="N5" s="379"/>
+      <c r="O5" s="379"/>
+      <c r="P5" s="379"/>
+      <c r="Q5" s="379"/>
+      <c r="R5" s="379"/>
+      <c r="S5" s="379"/>
+      <c r="T5" s="379"/>
+      <c r="U5" s="379"/>
+      <c r="V5" s="379"/>
+      <c r="W5" s="379"/>
+      <c r="X5" s="379"/>
+      <c r="Y5" s="379"/>
+      <c r="Z5" s="379"/>
+      <c r="AA5" s="379"/>
+      <c r="AB5" s="379"/>
+      <c r="AC5" s="379"/>
+      <c r="AD5" s="379"/>
+      <c r="AE5" s="379"/>
+      <c r="AF5" s="379"/>
+      <c r="AG5" s="379"/>
+      <c r="AH5" s="379"/>
+      <c r="AI5" s="379"/>
+      <c r="AJ5" s="379"/>
+      <c r="AK5" s="379"/>
+      <c r="AL5" s="379"/>
+      <c r="AM5" s="379"/>
+      <c r="AN5" s="379"/>
+      <c r="AO5" s="379"/>
+      <c r="AP5" s="379"/>
+      <c r="AQ5" s="379"/>
+      <c r="AR5" s="379"/>
+      <c r="AS5" s="379"/>
+      <c r="AT5" s="379"/>
+      <c r="AU5" s="379"/>
+      <c r="AV5" s="379"/>
+      <c r="AW5" s="379"/>
+      <c r="AX5" s="379"/>
+      <c r="AY5" s="379"/>
+      <c r="AZ5" s="379"/>
+      <c r="BA5" s="379"/>
+      <c r="BB5" s="379"/>
+      <c r="BC5" s="379"/>
+      <c r="BD5" s="379"/>
+      <c r="BE5" s="379"/>
+      <c r="BF5" s="379"/>
+      <c r="BG5" s="379"/>
+      <c r="BH5" s="379"/>
+      <c r="BI5" s="379"/>
+      <c r="BJ5" s="379"/>
+      <c r="BK5" s="379"/>
+      <c r="BL5" s="379"/>
+      <c r="BM5" s="379"/>
+      <c r="BN5" s="379"/>
+      <c r="BO5" s="379"/>
+      <c r="BP5" s="379"/>
+      <c r="BQ5" s="379"/>
+      <c r="BR5" s="379"/>
+      <c r="BS5" s="379"/>
+      <c r="BT5" s="379"/>
+      <c r="BU5" s="344"/>
+      <c r="BV5" s="344"/>
       <c r="BW5" s="344"/>
       <c r="BX5" s="344"/>
       <c r="BY5" s="344"/>
       <c r="BZ5" s="344"/>
-      <c r="CA5" s="344"/>
-      <c r="CB5" s="344"/>
-      <c r="CC5" s="381"/>
-      <c r="CD5" s="381"/>
+      <c r="CA5" s="378"/>
+      <c r="CB5" s="378"/>
     </row>
-    <row r="6" spans="1:87" s="345" customFormat="1" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A6" s="384"/>
-      <c r="B6" s="384"/>
-      <c r="C6" s="384"/>
-      <c r="D6" s="384"/>
-      <c r="E6" s="384"/>
-      <c r="F6" s="384"/>
-      <c r="G6" s="384"/>
-      <c r="H6" s="384"/>
-      <c r="I6" s="400"/>
-      <c r="K6" s="385"/>
-      <c r="L6" s="385"/>
-      <c r="M6" s="385"/>
-      <c r="N6" s="385"/>
-      <c r="O6" s="385"/>
-      <c r="P6" s="385"/>
-      <c r="Q6" s="385"/>
-      <c r="R6" s="385"/>
-      <c r="S6" s="385"/>
-      <c r="T6" s="385"/>
-      <c r="U6" s="385"/>
-      <c r="V6" s="385"/>
-      <c r="W6" s="385"/>
-      <c r="X6" s="385"/>
-      <c r="Y6" s="386"/>
-      <c r="Z6" s="386"/>
-      <c r="AA6" s="386"/>
-      <c r="AB6" s="386"/>
-      <c r="AC6" s="382"/>
-      <c r="AD6" s="384"/>
-      <c r="AE6" s="384"/>
-      <c r="AF6" s="384"/>
-      <c r="AG6" s="384"/>
-      <c r="AH6" s="384"/>
-      <c r="AI6" s="384"/>
-      <c r="AJ6" s="384"/>
-      <c r="AK6" s="384"/>
-      <c r="AL6" s="384"/>
-      <c r="AM6" s="384"/>
-      <c r="AN6" s="384"/>
-      <c r="AO6" s="384"/>
-      <c r="AP6" s="384"/>
-      <c r="AQ6" s="384"/>
-      <c r="AR6" s="384"/>
-      <c r="AS6" s="384"/>
-      <c r="AT6" s="384"/>
-      <c r="AU6" s="384"/>
-      <c r="AV6" s="384"/>
-      <c r="AW6" s="384"/>
-      <c r="AX6" s="384"/>
-      <c r="AY6" s="384"/>
-      <c r="AZ6" s="384"/>
-      <c r="BA6" s="384"/>
-      <c r="BB6" s="384"/>
-      <c r="BC6" s="384"/>
-      <c r="BD6" s="384"/>
-      <c r="BE6" s="384"/>
-      <c r="BF6" s="384"/>
-      <c r="BG6" s="384"/>
-      <c r="BH6" s="384"/>
-      <c r="BI6" s="384"/>
-      <c r="BJ6" s="384"/>
-      <c r="BK6" s="384"/>
-      <c r="BL6" s="384"/>
-      <c r="BM6" s="384"/>
-      <c r="BN6" s="384"/>
-      <c r="BO6" s="384"/>
-      <c r="BP6" s="384"/>
-      <c r="BQ6" s="384"/>
-      <c r="BR6" s="384"/>
-      <c r="BS6" s="384"/>
-      <c r="BT6" s="384"/>
-      <c r="BU6" s="384"/>
-      <c r="BV6" s="384"/>
+    <row r="6" spans="1:85" s="345" customFormat="1" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A6" s="381"/>
+      <c r="B6" s="381"/>
+      <c r="C6" s="381"/>
+      <c r="D6" s="381"/>
+      <c r="E6" s="381"/>
+      <c r="F6" s="381"/>
+      <c r="G6" s="381"/>
+      <c r="H6" s="381"/>
+      <c r="I6" s="394"/>
+      <c r="K6" s="382"/>
+      <c r="L6" s="382"/>
+      <c r="M6" s="382"/>
+      <c r="N6" s="382"/>
+      <c r="O6" s="382"/>
+      <c r="P6" s="382"/>
+      <c r="Q6" s="382"/>
+      <c r="R6" s="382"/>
+      <c r="S6" s="382"/>
+      <c r="T6" s="382"/>
+      <c r="U6" s="382"/>
+      <c r="V6" s="382"/>
+      <c r="W6" s="382"/>
+      <c r="X6" s="382"/>
+      <c r="Y6" s="383"/>
+      <c r="Z6" s="383"/>
+      <c r="AA6" s="383"/>
+      <c r="AB6" s="383"/>
+      <c r="AC6" s="379"/>
+      <c r="AD6" s="381"/>
+      <c r="AE6" s="381"/>
+      <c r="AF6" s="381"/>
+      <c r="AG6" s="381"/>
+      <c r="AH6" s="381"/>
+      <c r="AI6" s="381"/>
+      <c r="AJ6" s="381"/>
+      <c r="AK6" s="381"/>
+      <c r="AL6" s="381"/>
+      <c r="AM6" s="381"/>
+      <c r="AN6" s="381"/>
+      <c r="AO6" s="381"/>
+      <c r="AP6" s="381"/>
+      <c r="AQ6" s="381"/>
+      <c r="AR6" s="381"/>
+      <c r="AS6" s="381"/>
+      <c r="AT6" s="381"/>
+      <c r="AU6" s="381"/>
+      <c r="AV6" s="381"/>
+      <c r="AW6" s="381"/>
+      <c r="AX6" s="381"/>
+      <c r="AY6" s="381"/>
+      <c r="AZ6" s="381"/>
+      <c r="BA6" s="381"/>
+      <c r="BB6" s="381"/>
+      <c r="BC6" s="381"/>
+      <c r="BD6" s="381"/>
+      <c r="BE6" s="381"/>
+      <c r="BF6" s="381"/>
+      <c r="BG6" s="381"/>
+      <c r="BH6" s="381"/>
+      <c r="BI6" s="381"/>
+      <c r="BJ6" s="381"/>
+      <c r="BK6" s="381"/>
+      <c r="BL6" s="381"/>
+      <c r="BM6" s="381"/>
+      <c r="BN6" s="381"/>
+      <c r="BO6" s="381"/>
+      <c r="BP6" s="381"/>
+      <c r="BQ6" s="381"/>
+      <c r="BR6" s="381"/>
+      <c r="BS6" s="381"/>
+      <c r="BT6" s="381"/>
+      <c r="BU6" s="344"/>
+      <c r="BV6" s="344"/>
       <c r="BW6" s="344"/>
       <c r="BX6" s="344"/>
       <c r="BY6" s="344"/>
       <c r="BZ6" s="344"/>
-      <c r="CA6" s="344"/>
-      <c r="CB6" s="344"/>
-      <c r="CC6" s="381"/>
-      <c r="CD6" s="381"/>
+      <c r="CA6" s="378"/>
+      <c r="CB6" s="378"/>
     </row>
-    <row r="7" spans="1:87" s="345" customFormat="1" ht="12.75" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A7" s="401"/>
-      <c r="B7" s="402"/>
-      <c r="C7" s="401"/>
-      <c r="D7" s="402"/>
-      <c r="E7" s="402"/>
-      <c r="F7" s="403"/>
-      <c r="G7" s="402"/>
-      <c r="H7" s="402"/>
-      <c r="I7" s="400"/>
-      <c r="K7" s="404"/>
-      <c r="L7" s="404"/>
-      <c r="M7" s="404"/>
-      <c r="N7" s="404"/>
-      <c r="O7" s="404"/>
-      <c r="P7" s="404"/>
-      <c r="Q7" s="404"/>
-      <c r="R7" s="404"/>
-      <c r="S7" s="404"/>
-      <c r="T7" s="404"/>
-      <c r="U7" s="405"/>
-      <c r="V7" s="404"/>
-      <c r="W7" s="404"/>
-      <c r="X7" s="404"/>
-      <c r="Y7" s="386"/>
-      <c r="Z7" s="386"/>
-      <c r="AA7" s="386"/>
-      <c r="AB7" s="386"/>
-      <c r="AC7" s="382"/>
-      <c r="AD7" s="382"/>
-      <c r="AE7" s="382"/>
-      <c r="AF7" s="382"/>
-      <c r="AG7" s="382"/>
-      <c r="AH7" s="382"/>
-      <c r="AI7" s="382"/>
-      <c r="AJ7" s="382"/>
-      <c r="AK7" s="382"/>
-      <c r="AL7" s="382"/>
-      <c r="AM7" s="382"/>
-      <c r="AN7" s="382"/>
-      <c r="AO7" s="382"/>
-      <c r="AP7" s="382"/>
-      <c r="AQ7" s="382"/>
-      <c r="AR7" s="382"/>
-      <c r="AS7" s="382"/>
-      <c r="AT7" s="382"/>
-      <c r="AU7" s="382"/>
-      <c r="AV7" s="401"/>
-      <c r="AW7" s="401"/>
-      <c r="AX7" s="401"/>
-      <c r="AY7" s="402"/>
-      <c r="AZ7" s="401"/>
-      <c r="BA7" s="402"/>
-      <c r="BB7" s="402"/>
-      <c r="BC7" s="401"/>
-      <c r="BD7" s="401"/>
-      <c r="BE7" s="402"/>
-      <c r="BF7" s="402"/>
-      <c r="BG7" s="402"/>
-      <c r="BH7" s="402"/>
-      <c r="BI7" s="402"/>
-      <c r="BJ7" s="401"/>
-      <c r="BK7" s="401"/>
-      <c r="BL7" s="402"/>
-      <c r="BM7" s="401"/>
-      <c r="BN7" s="402"/>
-      <c r="BO7" s="402"/>
-      <c r="BP7" s="401"/>
-      <c r="BQ7" s="401"/>
-      <c r="BR7" s="401"/>
-      <c r="BS7" s="401"/>
-      <c r="BT7" s="402"/>
-      <c r="BU7" s="401"/>
-      <c r="BV7" s="401"/>
-      <c r="BW7" s="406"/>
-      <c r="BX7" s="406"/>
-      <c r="BY7" s="406"/>
-      <c r="BZ7" s="406"/>
-      <c r="CA7" s="406"/>
-      <c r="CB7" s="405"/>
-      <c r="CC7" s="405"/>
-      <c r="CD7" s="405"/>
+    <row r="7" spans="1:85" s="345" customFormat="1" ht="12.75" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A7" s="395"/>
+      <c r="B7" s="396"/>
+      <c r="C7" s="395"/>
+      <c r="D7" s="396"/>
+      <c r="E7" s="396"/>
+      <c r="F7" s="397"/>
+      <c r="G7" s="396"/>
+      <c r="H7" s="396"/>
+      <c r="I7" s="394"/>
+      <c r="K7" s="398"/>
+      <c r="L7" s="398"/>
+      <c r="M7" s="398"/>
+      <c r="N7" s="398"/>
+      <c r="O7" s="398"/>
+      <c r="P7" s="398"/>
+      <c r="Q7" s="398"/>
+      <c r="R7" s="398"/>
+      <c r="S7" s="398"/>
+      <c r="T7" s="398"/>
+      <c r="U7" s="399"/>
+      <c r="V7" s="398"/>
+      <c r="W7" s="398"/>
+      <c r="X7" s="398"/>
+      <c r="Y7" s="383"/>
+      <c r="Z7" s="383"/>
+      <c r="AA7" s="383"/>
+      <c r="AB7" s="383"/>
+      <c r="AC7" s="379"/>
+      <c r="AD7" s="379"/>
+      <c r="AE7" s="379"/>
+      <c r="AF7" s="379"/>
+      <c r="AG7" s="379"/>
+      <c r="AH7" s="379"/>
+      <c r="AI7" s="379"/>
+      <c r="AJ7" s="379"/>
+      <c r="AK7" s="379"/>
+      <c r="AL7" s="379"/>
+      <c r="AM7" s="379"/>
+      <c r="AN7" s="379"/>
+      <c r="AO7" s="379"/>
+      <c r="AP7" s="379"/>
+      <c r="AQ7" s="379"/>
+      <c r="AR7" s="379"/>
+      <c r="AS7" s="379"/>
+      <c r="AT7" s="379"/>
+      <c r="AU7" s="379"/>
+      <c r="AV7" s="395"/>
+      <c r="AW7" s="395"/>
+      <c r="AX7" s="395"/>
+      <c r="AY7" s="396"/>
+      <c r="AZ7" s="395"/>
+      <c r="BA7" s="396"/>
+      <c r="BB7" s="396"/>
+      <c r="BC7" s="395"/>
+      <c r="BD7" s="395"/>
+      <c r="BE7" s="396"/>
+      <c r="BF7" s="396"/>
+      <c r="BG7" s="396"/>
+      <c r="BH7" s="396"/>
+      <c r="BI7" s="396"/>
+      <c r="BJ7" s="395"/>
+      <c r="BK7" s="395"/>
+      <c r="BL7" s="396"/>
+      <c r="BM7" s="395"/>
+      <c r="BN7" s="396"/>
+      <c r="BO7" s="396"/>
+      <c r="BP7" s="395"/>
+      <c r="BQ7" s="395"/>
+      <c r="BR7" s="395"/>
+      <c r="BS7" s="395"/>
+      <c r="BT7" s="396"/>
+      <c r="BU7" s="400"/>
+      <c r="BV7" s="400"/>
+      <c r="BW7" s="400"/>
+      <c r="BX7" s="400"/>
+      <c r="BY7" s="400"/>
+      <c r="BZ7" s="399"/>
+      <c r="CA7" s="399"/>
+      <c r="CB7" s="399"/>
     </row>
-    <row r="8" spans="1:87" s="409" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="448" t="s">
+    <row r="8" spans="1:85" s="402" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A8" s="439" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="449" t="s">
+      <c r="B8" s="440" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="450" t="s">
+      <c r="C8" s="441" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="451" t="s">
+      <c r="D8" s="442" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="451" t="s">
+      <c r="E8" s="442" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="452" t="s">
+      <c r="F8" s="443" t="s">
         <v>142</v>
       </c>
       <c r="G8" s="268" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="453" t="s">
+      <c r="H8" s="444" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="453" t="s">
+      <c r="I8" s="444" t="s">
         <v>12</v>
       </c>
       <c r="J8" s="268" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="464" t="s">
+      <c r="K8" s="455" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="479"/>
-      <c r="M8" s="479"/>
-      <c r="N8" s="479"/>
-      <c r="O8" s="479"/>
-      <c r="P8" s="479"/>
-      <c r="Q8" s="479"/>
-      <c r="R8" s="479"/>
-      <c r="S8" s="479"/>
-      <c r="T8" s="479"/>
-      <c r="U8" s="479"/>
-      <c r="V8" s="479"/>
-      <c r="W8" s="479"/>
-      <c r="X8" s="479"/>
-      <c r="Y8" s="463" t="s">
+      <c r="L8" s="470"/>
+      <c r="M8" s="470"/>
+      <c r="N8" s="470"/>
+      <c r="O8" s="470"/>
+      <c r="P8" s="470"/>
+      <c r="Q8" s="470"/>
+      <c r="R8" s="470"/>
+      <c r="S8" s="470"/>
+      <c r="T8" s="470"/>
+      <c r="U8" s="470"/>
+      <c r="V8" s="470"/>
+      <c r="W8" s="470"/>
+      <c r="X8" s="470"/>
+      <c r="Y8" s="454" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="479"/>
-      <c r="AA8" s="479"/>
-      <c r="AB8" s="479"/>
-      <c r="AC8" s="479"/>
-      <c r="AD8" s="479"/>
-      <c r="AE8" s="479"/>
-      <c r="AF8" s="479"/>
-      <c r="AG8" s="479"/>
-      <c r="AH8" s="479"/>
-      <c r="AI8" s="479"/>
-      <c r="AJ8" s="479"/>
-      <c r="AK8" s="479"/>
-      <c r="AL8" s="479"/>
-      <c r="AM8" s="479"/>
-      <c r="AN8" s="479"/>
-      <c r="AO8" s="480"/>
+      <c r="Z8" s="470"/>
+      <c r="AA8" s="470"/>
+      <c r="AB8" s="470"/>
+      <c r="AC8" s="470"/>
+      <c r="AD8" s="470"/>
+      <c r="AE8" s="470"/>
+      <c r="AF8" s="470"/>
+      <c r="AG8" s="470"/>
+      <c r="AH8" s="470"/>
+      <c r="AI8" s="470"/>
+      <c r="AJ8" s="470"/>
+      <c r="AK8" s="470"/>
+      <c r="AL8" s="470"/>
+      <c r="AM8" s="470"/>
+      <c r="AN8" s="470"/>
+      <c r="AO8" s="471"/>
       <c r="AP8" s="268" t="s">
         <v>16</v>
       </c>
@@ -15594,170 +15553,166 @@
       <c r="AU8" s="268" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="481" t="s">
+      <c r="AV8" s="472" t="s">
         <v>22</v>
       </c>
       <c r="AW8" s="262" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="262" t="s">
+      <c r="AX8" s="472" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="462" t="s">
+      <c r="AY8" s="453" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="479"/>
-      <c r="BA8" s="479"/>
-      <c r="BB8" s="479"/>
-      <c r="BC8" s="479"/>
-      <c r="BD8" s="479"/>
-      <c r="BE8" s="479"/>
-      <c r="BF8" s="479"/>
-      <c r="BG8" s="479"/>
-      <c r="BH8" s="479"/>
-      <c r="BI8" s="479"/>
-      <c r="BJ8" s="479"/>
-      <c r="BK8" s="479"/>
-      <c r="BL8" s="479"/>
-      <c r="BM8" s="479"/>
-      <c r="BN8" s="479"/>
-      <c r="BO8" s="479"/>
-      <c r="BP8" s="480"/>
-      <c r="BQ8" s="407" t="s">
+      <c r="AZ8" s="470"/>
+      <c r="BA8" s="470"/>
+      <c r="BB8" s="470"/>
+      <c r="BC8" s="470"/>
+      <c r="BD8" s="470"/>
+      <c r="BE8" s="470"/>
+      <c r="BF8" s="470"/>
+      <c r="BG8" s="470"/>
+      <c r="BH8" s="470"/>
+      <c r="BI8" s="470"/>
+      <c r="BJ8" s="470"/>
+      <c r="BK8" s="470"/>
+      <c r="BL8" s="470"/>
+      <c r="BM8" s="470"/>
+      <c r="BN8" s="470"/>
+      <c r="BO8" s="470"/>
+      <c r="BP8" s="471"/>
+      <c r="BQ8" s="401" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="389"/>
-      <c r="BS8" s="450" t="s">
+      <c r="BR8" s="386"/>
+      <c r="BS8" s="441" t="s">
         <v>143</v>
       </c>
-      <c r="BT8" s="450" t="s">
+      <c r="BT8" s="441" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="408" t="s">
-        <v>28</v>
-      </c>
-      <c r="BV8" s="402"/>
-      <c r="BW8" s="499" t="s">
+      <c r="BU8" s="490" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="475" t="s">
+      <c r="BV8" s="466" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="482"/>
-      <c r="BZ8" s="482"/>
-      <c r="CA8" s="483"/>
-      <c r="CB8" s="283" t="s">
+      <c r="BW8" s="473"/>
+      <c r="BX8" s="473"/>
+      <c r="BY8" s="474"/>
+      <c r="BZ8" s="283" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="283" t="s">
+      <c r="CA8" s="283" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="239" t="s">
+      <c r="CB8" s="239" t="s">
         <v>33</v>
       </c>
-      <c r="CH8" s="346"/>
-      <c r="CI8" s="346"/>
+      <c r="CF8" s="346"/>
+      <c r="CG8" s="346"/>
     </row>
-    <row r="9" spans="1:87" s="409" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="484"/>
-      <c r="B9" s="484"/>
-      <c r="C9" s="484"/>
-      <c r="D9" s="484"/>
-      <c r="E9" s="484"/>
-      <c r="F9" s="484"/>
+    <row r="9" spans="1:85" s="402" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A9" s="475"/>
+      <c r="B9" s="475"/>
+      <c r="C9" s="475"/>
+      <c r="D9" s="475"/>
+      <c r="E9" s="475"/>
+      <c r="F9" s="475"/>
       <c r="G9" s="240"/>
-      <c r="H9" s="484"/>
-      <c r="I9" s="484"/>
+      <c r="H9" s="475"/>
+      <c r="I9" s="475"/>
       <c r="J9" s="240"/>
-      <c r="K9" s="454" t="s">
+      <c r="K9" s="445" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="454" t="s">
+      <c r="L9" s="445" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="454" t="s">
+      <c r="M9" s="445" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="454" t="s">
+      <c r="N9" s="445" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="454" t="s">
+      <c r="O9" s="445" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="454" t="s">
+      <c r="P9" s="445" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="454" t="s">
+      <c r="Q9" s="445" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="454" t="s">
+      <c r="R9" s="445" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="454" t="s">
+      <c r="S9" s="445" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="454" t="s">
+      <c r="T9" s="445" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="454" t="s">
+      <c r="U9" s="445" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="410" t="s">
+      <c r="V9" s="403" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="389"/>
-      <c r="X9" s="454" t="s">
+      <c r="W9" s="386"/>
+      <c r="X9" s="445" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="456" t="s">
+      <c r="Y9" s="447" t="s">
         <v>47</v>
       </c>
-      <c r="Z9" s="456" t="s">
+      <c r="Z9" s="447" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="456" t="s">
+      <c r="AA9" s="447" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="456" t="s">
+      <c r="AB9" s="447" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="456" t="s">
+      <c r="AC9" s="447" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="456" t="s">
+      <c r="AD9" s="447" t="s">
         <v>144</v>
       </c>
-      <c r="AE9" s="456" t="s">
+      <c r="AE9" s="447" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="456" t="s">
+      <c r="AF9" s="447" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="456" t="s">
+      <c r="AG9" s="447" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="456" t="s">
+      <c r="AH9" s="447" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="456" t="s">
+      <c r="AI9" s="447" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="485" t="s">
+      <c r="AJ9" s="476" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="486" t="s">
+      <c r="AK9" s="477" t="s">
         <v>59</v>
       </c>
       <c r="AL9" s="262" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="487" t="s">
+      <c r="AM9" s="478" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="481" t="s">
+      <c r="AN9" s="472" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="481" t="s">
+      <c r="AO9" s="472" t="s">
         <v>63</v>
       </c>
       <c r="AP9" s="240"/>
@@ -15768,88 +15723,86 @@
       <c r="AU9" s="240"/>
       <c r="AV9" s="260"/>
       <c r="AW9" s="240"/>
-      <c r="AX9" s="240"/>
-      <c r="AY9" s="390" t="s">
+      <c r="AX9" s="260"/>
+      <c r="AY9" s="387" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="387"/>
-      <c r="BA9" s="387"/>
-      <c r="BB9" s="387"/>
-      <c r="BC9" s="387"/>
-      <c r="BD9" s="387"/>
-      <c r="BE9" s="387"/>
-      <c r="BF9" s="387"/>
-      <c r="BG9" s="387"/>
-      <c r="BH9" s="387"/>
-      <c r="BI9" s="387"/>
-      <c r="BJ9" s="388"/>
-      <c r="BK9" s="390" t="s">
+      <c r="AZ9" s="384"/>
+      <c r="BA9" s="384"/>
+      <c r="BB9" s="384"/>
+      <c r="BC9" s="384"/>
+      <c r="BD9" s="384"/>
+      <c r="BE9" s="384"/>
+      <c r="BF9" s="384"/>
+      <c r="BG9" s="384"/>
+      <c r="BH9" s="384"/>
+      <c r="BI9" s="384"/>
+      <c r="BJ9" s="385"/>
+      <c r="BK9" s="387" t="s">
         <v>64</v>
       </c>
-      <c r="BL9" s="387"/>
-      <c r="BM9" s="387"/>
-      <c r="BN9" s="387"/>
-      <c r="BO9" s="387"/>
-      <c r="BP9" s="388"/>
-      <c r="BQ9" s="461" t="s">
+      <c r="BL9" s="384"/>
+      <c r="BM9" s="384"/>
+      <c r="BN9" s="384"/>
+      <c r="BO9" s="384"/>
+      <c r="BP9" s="385"/>
+      <c r="BQ9" s="452" t="s">
         <v>65</v>
       </c>
-      <c r="BR9" s="461" t="s">
+      <c r="BR9" s="452" t="s">
         <v>66</v>
       </c>
-      <c r="BS9" s="484"/>
-      <c r="BT9" s="484"/>
-      <c r="BU9" s="391"/>
-      <c r="BV9" s="402"/>
-      <c r="BW9" s="500"/>
-      <c r="BX9" s="488"/>
-      <c r="BY9" s="476"/>
-      <c r="BZ9" s="476"/>
-      <c r="CA9" s="489"/>
-      <c r="CB9" s="484"/>
-      <c r="CC9" s="484"/>
-      <c r="CD9" s="240"/>
-      <c r="CH9" s="346"/>
-      <c r="CI9" s="346"/>
+      <c r="BS9" s="475"/>
+      <c r="BT9" s="475"/>
+      <c r="BU9" s="491"/>
+      <c r="BV9" s="479"/>
+      <c r="BW9" s="467"/>
+      <c r="BX9" s="467"/>
+      <c r="BY9" s="480"/>
+      <c r="BZ9" s="475"/>
+      <c r="CA9" s="475"/>
+      <c r="CB9" s="240"/>
+      <c r="CF9" s="346"/>
+      <c r="CG9" s="346"/>
     </row>
-    <row r="10" spans="1:87" s="399" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="484"/>
-      <c r="B10" s="484"/>
-      <c r="C10" s="484"/>
-      <c r="D10" s="484"/>
-      <c r="E10" s="484"/>
-      <c r="F10" s="484"/>
+    <row r="10" spans="1:85" s="393" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A10" s="475"/>
+      <c r="B10" s="475"/>
+      <c r="C10" s="475"/>
+      <c r="D10" s="475"/>
+      <c r="E10" s="475"/>
+      <c r="F10" s="475"/>
       <c r="G10" s="240"/>
-      <c r="H10" s="484"/>
-      <c r="I10" s="484"/>
+      <c r="H10" s="475"/>
+      <c r="I10" s="475"/>
       <c r="J10" s="240"/>
-      <c r="K10" s="484"/>
-      <c r="L10" s="484"/>
-      <c r="M10" s="484"/>
-      <c r="N10" s="484"/>
-      <c r="O10" s="484"/>
-      <c r="P10" s="484"/>
-      <c r="Q10" s="484"/>
-      <c r="R10" s="484"/>
-      <c r="S10" s="484"/>
-      <c r="T10" s="484"/>
-      <c r="U10" s="484"/>
-      <c r="V10" s="392"/>
-      <c r="W10" s="393"/>
-      <c r="X10" s="484"/>
-      <c r="Y10" s="484"/>
-      <c r="Z10" s="484"/>
-      <c r="AA10" s="484"/>
-      <c r="AB10" s="484"/>
-      <c r="AC10" s="484"/>
-      <c r="AD10" s="484"/>
-      <c r="AE10" s="484"/>
-      <c r="AF10" s="484"/>
-      <c r="AG10" s="484"/>
-      <c r="AH10" s="484"/>
-      <c r="AI10" s="484"/>
+      <c r="K10" s="475"/>
+      <c r="L10" s="475"/>
+      <c r="M10" s="475"/>
+      <c r="N10" s="475"/>
+      <c r="O10" s="475"/>
+      <c r="P10" s="475"/>
+      <c r="Q10" s="475"/>
+      <c r="R10" s="475"/>
+      <c r="S10" s="475"/>
+      <c r="T10" s="475"/>
+      <c r="U10" s="475"/>
+      <c r="V10" s="388"/>
+      <c r="W10" s="389"/>
+      <c r="X10" s="475"/>
+      <c r="Y10" s="475"/>
+      <c r="Z10" s="475"/>
+      <c r="AA10" s="475"/>
+      <c r="AB10" s="475"/>
+      <c r="AC10" s="475"/>
+      <c r="AD10" s="475"/>
+      <c r="AE10" s="475"/>
+      <c r="AF10" s="475"/>
+      <c r="AG10" s="475"/>
+      <c r="AH10" s="475"/>
+      <c r="AI10" s="475"/>
       <c r="AJ10" s="240"/>
-      <c r="AK10" s="490"/>
+      <c r="AK10" s="481"/>
       <c r="AL10" s="240"/>
       <c r="AM10" s="260"/>
       <c r="AN10" s="260"/>
@@ -15862,123 +15815,121 @@
       <c r="AU10" s="240"/>
       <c r="AV10" s="260"/>
       <c r="AW10" s="240"/>
-      <c r="AX10" s="240"/>
-      <c r="AY10" s="457" t="s">
+      <c r="AX10" s="260"/>
+      <c r="AY10" s="448" t="s">
         <v>67</v>
       </c>
-      <c r="AZ10" s="457" t="s">
+      <c r="AZ10" s="448" t="s">
         <v>68</v>
       </c>
-      <c r="BA10" s="457" t="s">
+      <c r="BA10" s="448" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="458" t="s">
+      <c r="BB10" s="449" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="497" t="s">
+      <c r="BC10" s="488" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="497" t="s">
+      <c r="BD10" s="488" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="459" t="s">
+      <c r="BE10" s="450" t="s">
         <v>145</v>
       </c>
-      <c r="BF10" s="459" t="s">
+      <c r="BF10" s="450" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="459" t="s">
+      <c r="BG10" s="450" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="497" t="s">
+      <c r="BH10" s="488" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="459" t="s">
+      <c r="BI10" s="450" t="s">
         <v>79</v>
       </c>
-      <c r="BJ10" s="460" t="s">
+      <c r="BJ10" s="451" t="s">
         <v>80</v>
       </c>
-      <c r="BK10" s="497" t="s">
+      <c r="BK10" s="488" t="s">
         <v>81</v>
       </c>
-      <c r="BL10" s="498" t="s">
+      <c r="BL10" s="489" t="s">
         <v>82</v>
       </c>
-      <c r="BM10" s="497" t="s">
+      <c r="BM10" s="488" t="s">
         <v>83</v>
       </c>
-      <c r="BN10" s="498" t="s">
+      <c r="BN10" s="489" t="s">
         <v>84</v>
       </c>
-      <c r="BO10" s="498" t="s">
+      <c r="BO10" s="489" t="s">
         <v>146</v>
       </c>
-      <c r="BP10" s="450" t="s">
+      <c r="BP10" s="441" t="s">
         <v>85</v>
       </c>
-      <c r="BQ10" s="484"/>
-      <c r="BR10" s="484"/>
-      <c r="BS10" s="484"/>
-      <c r="BT10" s="484"/>
-      <c r="BU10" s="391"/>
-      <c r="BV10" s="402"/>
-      <c r="BW10" s="500"/>
-      <c r="BX10" s="491"/>
-      <c r="BY10" s="492"/>
-      <c r="BZ10" s="492"/>
-      <c r="CA10" s="493"/>
-      <c r="CB10" s="484"/>
-      <c r="CC10" s="484"/>
-      <c r="CD10" s="240"/>
-      <c r="CE10" s="228" t="s">
+      <c r="BQ10" s="475"/>
+      <c r="BR10" s="475"/>
+      <c r="BS10" s="475"/>
+      <c r="BT10" s="475"/>
+      <c r="BU10" s="491"/>
+      <c r="BV10" s="482"/>
+      <c r="BW10" s="483"/>
+      <c r="BX10" s="483"/>
+      <c r="BY10" s="484"/>
+      <c r="BZ10" s="475"/>
+      <c r="CA10" s="475"/>
+      <c r="CB10" s="240"/>
+      <c r="CC10" s="228" t="s">
         <v>3</v>
       </c>
-      <c r="CH10" s="346"/>
-      <c r="CI10" s="346"/>
+      <c r="CF10" s="346"/>
+      <c r="CG10" s="346"/>
     </row>
-    <row r="11" spans="1:87" s="399" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="494"/>
-      <c r="B11" s="494"/>
-      <c r="C11" s="494"/>
-      <c r="D11" s="494"/>
-      <c r="E11" s="494"/>
-      <c r="F11" s="494"/>
+    <row r="11" spans="1:85" s="393" customFormat="1" ht="38.25" customHeight="1">
+      <c r="A11" s="485"/>
+      <c r="B11" s="485"/>
+      <c r="C11" s="485"/>
+      <c r="D11" s="485"/>
+      <c r="E11" s="485"/>
+      <c r="F11" s="485"/>
       <c r="G11" s="263"/>
-      <c r="H11" s="494"/>
-      <c r="I11" s="494"/>
+      <c r="H11" s="485"/>
+      <c r="I11" s="485"/>
       <c r="J11" s="263"/>
-      <c r="K11" s="494"/>
-      <c r="L11" s="494"/>
-      <c r="M11" s="494"/>
-      <c r="N11" s="494"/>
-      <c r="O11" s="494"/>
-      <c r="P11" s="494"/>
-      <c r="Q11" s="494"/>
-      <c r="R11" s="494"/>
-      <c r="S11" s="494"/>
-      <c r="T11" s="494"/>
-      <c r="U11" s="494"/>
-      <c r="V11" s="455" t="s">
+      <c r="K11" s="485"/>
+      <c r="L11" s="485"/>
+      <c r="M11" s="485"/>
+      <c r="N11" s="485"/>
+      <c r="O11" s="485"/>
+      <c r="P11" s="485"/>
+      <c r="Q11" s="485"/>
+      <c r="R11" s="485"/>
+      <c r="S11" s="485"/>
+      <c r="T11" s="485"/>
+      <c r="U11" s="485"/>
+      <c r="V11" s="446" t="s">
         <v>86</v>
       </c>
-      <c r="W11" s="455" t="s">
+      <c r="W11" s="446" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="494"/>
-      <c r="Y11" s="494"/>
-      <c r="Z11" s="494"/>
-      <c r="AA11" s="494"/>
-      <c r="AB11" s="494"/>
-      <c r="AC11" s="494"/>
-      <c r="AD11" s="494"/>
-      <c r="AE11" s="494"/>
-      <c r="AF11" s="494"/>
-      <c r="AG11" s="494"/>
-      <c r="AH11" s="494"/>
-      <c r="AI11" s="494"/>
+      <c r="X11" s="485"/>
+      <c r="Y11" s="485"/>
+      <c r="Z11" s="485"/>
+      <c r="AA11" s="485"/>
+      <c r="AB11" s="485"/>
+      <c r="AC11" s="485"/>
+      <c r="AD11" s="485"/>
+      <c r="AE11" s="485"/>
+      <c r="AF11" s="485"/>
+      <c r="AG11" s="485"/>
+      <c r="AH11" s="485"/>
+      <c r="AI11" s="485"/>
       <c r="AJ11" s="263"/>
-      <c r="AK11" s="495"/>
+      <c r="AK11" s="486"/>
       <c r="AL11" s="263"/>
       <c r="AM11" s="261"/>
       <c r="AN11" s="261"/>
@@ -15991,461 +15942,452 @@
       <c r="AU11" s="263"/>
       <c r="AV11" s="261"/>
       <c r="AW11" s="263"/>
-      <c r="AX11" s="263"/>
-      <c r="AY11" s="478" t="s">
+      <c r="AX11" s="261"/>
+      <c r="AY11" s="469" t="s">
         <v>88</v>
       </c>
-      <c r="AZ11" s="478" t="s">
+      <c r="AZ11" s="469" t="s">
         <v>89</v>
       </c>
-      <c r="BA11" s="478" t="s">
+      <c r="BA11" s="469" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="494"/>
+      <c r="BB11" s="485"/>
       <c r="BC11" s="263"/>
       <c r="BD11" s="263"/>
-      <c r="BE11" s="494"/>
-      <c r="BF11" s="494"/>
-      <c r="BG11" s="494"/>
+      <c r="BE11" s="485"/>
+      <c r="BF11" s="485"/>
+      <c r="BG11" s="485"/>
       <c r="BH11" s="263"/>
-      <c r="BI11" s="494"/>
-      <c r="BJ11" s="494"/>
+      <c r="BI11" s="485"/>
+      <c r="BJ11" s="485"/>
       <c r="BK11" s="263"/>
       <c r="BL11" s="263"/>
       <c r="BM11" s="263"/>
       <c r="BN11" s="263"/>
       <c r="BO11" s="263"/>
-      <c r="BP11" s="494"/>
-      <c r="BQ11" s="494"/>
-      <c r="BR11" s="494"/>
-      <c r="BS11" s="494"/>
-      <c r="BT11" s="494"/>
-      <c r="BU11" s="392"/>
-      <c r="BV11" s="402"/>
-      <c r="BW11" s="501"/>
-      <c r="BX11" s="502" t="s">
+      <c r="BP11" s="485"/>
+      <c r="BQ11" s="485"/>
+      <c r="BR11" s="485"/>
+      <c r="BS11" s="485"/>
+      <c r="BT11" s="485"/>
+      <c r="BU11" s="492"/>
+      <c r="BV11" s="493" t="s">
         <v>91</v>
       </c>
-      <c r="BY11" s="502" t="s">
+      <c r="BW11" s="493" t="s">
         <v>92</v>
       </c>
-      <c r="BZ11" s="502" t="s">
+      <c r="BX11" s="493" t="s">
         <v>93</v>
       </c>
-      <c r="CA11" s="503" t="s">
+      <c r="BY11" s="494" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="496"/>
-      <c r="CC11" s="496"/>
-      <c r="CD11" s="241"/>
-      <c r="CE11" s="477">
+      <c r="BZ11" s="487"/>
+      <c r="CA11" s="487"/>
+      <c r="CB11" s="241"/>
+      <c r="CC11" s="468">
         <v>25</v>
       </c>
-      <c r="CF11" s="411"/>
-      <c r="CH11" s="346"/>
-      <c r="CI11" s="346"/>
+      <c r="CD11" s="404"/>
+      <c r="CF11" s="346"/>
+      <c r="CG11" s="346"/>
     </row>
-    <row r="12" spans="1:87" s="398" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="412">
+    <row r="12" spans="1:85" s="392" customFormat="1" ht="15" customHeight="1">
+      <c r="A12" s="405">
         <v>1</v>
       </c>
-      <c r="B12" s="394">
+      <c r="B12" s="390">
         <f>A12+1</f>
         <v>2</v>
       </c>
-      <c r="C12" s="394">
+      <c r="C12" s="390">
         <f>B12+1</f>
         <v>3</v>
       </c>
-      <c r="D12" s="394">
+      <c r="D12" s="390">
         <f>C12+1</f>
         <v>4</v>
       </c>
-      <c r="E12" s="394"/>
-      <c r="F12" s="394">
+      <c r="E12" s="390"/>
+      <c r="F12" s="390">
         <f>D12+1</f>
         <v>5</v>
       </c>
-      <c r="G12" s="394">
+      <c r="G12" s="390">
         <f t="shared" ref="G12:AV12" si="0">F12+1</f>
         <v>6</v>
       </c>
-      <c r="H12" s="394">
+      <c r="H12" s="390">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I12" s="394">
+      <c r="I12" s="390">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J12" s="394">
+      <c r="J12" s="390">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K12" s="394">
+      <c r="K12" s="390">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L12" s="394">
+      <c r="L12" s="390">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="M12" s="394">
+      <c r="M12" s="390">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="N12" s="394">
+      <c r="N12" s="390">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="O12" s="394">
+      <c r="O12" s="390">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="P12" s="394">
+      <c r="P12" s="390">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="Q12" s="394">
+      <c r="Q12" s="390">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="R12" s="394">
+      <c r="R12" s="390">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="S12" s="394">
+      <c r="S12" s="390">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="T12" s="394">
+      <c r="T12" s="390">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="U12" s="394">
+      <c r="U12" s="390">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="V12" s="394">
+      <c r="V12" s="390">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="W12" s="394">
+      <c r="W12" s="390">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="X12" s="394">
+      <c r="X12" s="390">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="Y12" s="394">
+      <c r="Y12" s="390">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="Z12" s="394">
+      <c r="Z12" s="390">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="AA12" s="394">
+      <c r="AA12" s="390">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="AB12" s="394">
+      <c r="AB12" s="390">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="AC12" s="394">
+      <c r="AC12" s="390">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="AD12" s="394">
+      <c r="AD12" s="390">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="AE12" s="394">
+      <c r="AE12" s="390">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="AF12" s="394">
+      <c r="AF12" s="390">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="AG12" s="394">
+      <c r="AG12" s="390">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="AH12" s="394">
+      <c r="AH12" s="390">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="AI12" s="394">
+      <c r="AI12" s="390">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="AJ12" s="394">
+      <c r="AJ12" s="390">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="AK12" s="394">
+      <c r="AK12" s="390">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="AL12" s="394">
+      <c r="AL12" s="390">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="AM12" s="394">
+      <c r="AM12" s="390">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="AN12" s="394">
+      <c r="AN12" s="390">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="AO12" s="394">
+      <c r="AO12" s="390">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="AP12" s="394">
+      <c r="AP12" s="390">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="AQ12" s="394">
+      <c r="AQ12" s="390">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="AR12" s="394">
+      <c r="AR12" s="390">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="AS12" s="394">
+      <c r="AS12" s="390">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="AT12" s="394">
+      <c r="AT12" s="390">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="AU12" s="394">
+      <c r="AU12" s="390">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="AV12" s="394">
+      <c r="AV12" s="390">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="AW12" s="394"/>
-      <c r="AX12" s="394"/>
-      <c r="AY12" s="394">
+      <c r="AW12" s="390"/>
+      <c r="AX12" s="390"/>
+      <c r="AY12" s="390">
         <f>AV12+1</f>
         <v>48</v>
       </c>
-      <c r="AZ12" s="394">
+      <c r="AZ12" s="390">
         <f t="shared" ref="AZ12:BE12" si="1">AY12+1</f>
         <v>49</v>
       </c>
-      <c r="BA12" s="394">
+      <c r="BA12" s="390">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="BB12" s="394">
+      <c r="BB12" s="390">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="BC12" s="394">
+      <c r="BC12" s="390">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="BD12" s="394">
+      <c r="BD12" s="390">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="BE12" s="394">
+      <c r="BE12" s="390">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="BF12" s="394"/>
-      <c r="BG12" s="394"/>
-      <c r="BH12" s="394"/>
-      <c r="BI12" s="394"/>
-      <c r="BJ12" s="394">
+      <c r="BF12" s="390"/>
+      <c r="BG12" s="390"/>
+      <c r="BH12" s="390"/>
+      <c r="BI12" s="390"/>
+      <c r="BJ12" s="390">
         <f>BE12+1</f>
         <v>55</v>
       </c>
-      <c r="BK12" s="394">
+      <c r="BK12" s="390">
         <f>BJ12+1</f>
         <v>56</v>
       </c>
-      <c r="BL12" s="394">
+      <c r="BL12" s="390">
         <f>BK12+1</f>
         <v>57</v>
       </c>
-      <c r="BM12" s="394">
+      <c r="BM12" s="390">
         <f>BL12+1</f>
         <v>58</v>
       </c>
-      <c r="BN12" s="394">
+      <c r="BN12" s="390">
         <f>BM12+1</f>
         <v>59</v>
       </c>
-      <c r="BO12" s="394"/>
-      <c r="BP12" s="394">
+      <c r="BO12" s="390"/>
+      <c r="BP12" s="390">
         <f>BN12+1</f>
         <v>60</v>
       </c>
-      <c r="BQ12" s="394">
+      <c r="BQ12" s="390">
         <f>BP12+1</f>
         <v>61</v>
       </c>
-      <c r="BR12" s="394">
+      <c r="BR12" s="390">
         <f>BQ12+1</f>
         <v>62</v>
       </c>
-      <c r="BS12" s="394"/>
-      <c r="BT12" s="394">
+      <c r="BS12" s="390"/>
+      <c r="BT12" s="390">
         <f>BR12+1</f>
         <v>63</v>
       </c>
-      <c r="BU12" s="394">
-        <f>BT12+1</f>
-        <v>64</v>
-      </c>
-      <c r="BV12" s="396"/>
-      <c r="BW12" s="397" t="s">
+      <c r="BU12" s="391" t="s">
         <v>95</v>
       </c>
-      <c r="BX12" s="394">
-        <f t="shared" ref="BX12:CD12" si="2">BW12+1</f>
+      <c r="BV12" s="390">
+        <f t="shared" ref="BV12:CB12" si="2">BU12+1</f>
         <v>66</v>
       </c>
-      <c r="BY12" s="394">
+      <c r="BW12" s="390">
         <f t="shared" si="2"/>
         <v>67</v>
       </c>
-      <c r="BZ12" s="394">
+      <c r="BX12" s="390">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="CA12" s="394">
+      <c r="BY12" s="390">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
-      <c r="CB12" s="394">
+      <c r="BZ12" s="390">
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="CC12" s="394">
+      <c r="CA12" s="390">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="CD12" s="394">
+      <c r="CB12" s="390">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="CG12" s="399"/>
-      <c r="CH12" s="346"/>
-      <c r="CI12" s="346"/>
+      <c r="CE12" s="393"/>
+      <c r="CF12" s="346"/>
+      <c r="CG12" s="346"/>
     </row>
-    <row r="13" spans="1:87" s="398" customFormat="1" ht="15" customHeight="1">
-      <c r="A13" s="412" t="s">
+    <row r="13" spans="1:85" s="392" customFormat="1" ht="15" customHeight="1">
+      <c r="A13" s="405" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="412" t="s">
+      <c r="B13" s="405" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="412" t="s">
+      <c r="C13" s="405" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="394"/>
-      <c r="E13" s="394"/>
-      <c r="F13" s="394"/>
-      <c r="G13" s="412" t="s">
+      <c r="D13" s="390"/>
+      <c r="E13" s="390"/>
+      <c r="F13" s="390"/>
+      <c r="G13" s="405" t="s">
         <v>96</v>
       </c>
-      <c r="H13" s="412" t="s">
+      <c r="H13" s="405" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="412" t="s">
+      <c r="I13" s="405" t="s">
         <v>96</v>
       </c>
-      <c r="J13" s="394"/>
-      <c r="K13" s="394"/>
-      <c r="L13" s="394"/>
-      <c r="M13" s="394"/>
-      <c r="N13" s="394"/>
-      <c r="O13" s="394"/>
-      <c r="P13" s="394"/>
-      <c r="Q13" s="394"/>
-      <c r="R13" s="394"/>
-      <c r="S13" s="394"/>
-      <c r="T13" s="394"/>
-      <c r="U13" s="394"/>
-      <c r="V13" s="394"/>
-      <c r="W13" s="394"/>
-      <c r="X13" s="394"/>
-      <c r="Y13" s="394"/>
-      <c r="Z13" s="394"/>
-      <c r="AA13" s="394"/>
-      <c r="AB13" s="394"/>
-      <c r="AC13" s="394"/>
-      <c r="AD13" s="394"/>
-      <c r="AE13" s="394"/>
-      <c r="AF13" s="394"/>
-      <c r="AG13" s="394"/>
-      <c r="AH13" s="394"/>
-      <c r="AI13" s="394"/>
-      <c r="AJ13" s="394"/>
-      <c r="AK13" s="394"/>
-      <c r="AL13" s="394"/>
-      <c r="AM13" s="394"/>
-      <c r="AN13" s="394"/>
-      <c r="AO13" s="394"/>
-      <c r="AP13" s="394"/>
-      <c r="AQ13" s="394"/>
-      <c r="AR13" s="394"/>
-      <c r="AS13" s="394"/>
-      <c r="AT13" s="394"/>
-      <c r="AU13" s="394"/>
-      <c r="AV13" s="394"/>
-      <c r="AW13" s="394"/>
-      <c r="AX13" s="394"/>
-      <c r="AY13" s="394"/>
-      <c r="AZ13" s="394"/>
-      <c r="BA13" s="394"/>
-      <c r="BB13" s="394"/>
-      <c r="BC13" s="394"/>
-      <c r="BD13" s="394"/>
-      <c r="BE13" s="394"/>
-      <c r="BF13" s="394"/>
-      <c r="BG13" s="394"/>
-      <c r="BH13" s="394"/>
-      <c r="BI13" s="394"/>
-      <c r="BJ13" s="394"/>
-      <c r="BK13" s="394"/>
-      <c r="BL13" s="394"/>
-      <c r="BM13" s="394"/>
-      <c r="BN13" s="394"/>
-      <c r="BO13" s="394"/>
-      <c r="BP13" s="394"/>
-      <c r="BQ13" s="394"/>
-      <c r="BR13" s="394"/>
-      <c r="BS13" s="394"/>
-      <c r="BT13" s="394"/>
-      <c r="BU13" s="395"/>
-      <c r="BV13" s="396"/>
-      <c r="BW13" s="397"/>
-      <c r="BX13" s="394"/>
-      <c r="BY13" s="394"/>
-      <c r="BZ13" s="394"/>
-      <c r="CA13" s="394"/>
-      <c r="CB13" s="394"/>
-      <c r="CC13" s="394"/>
-      <c r="CD13" s="394"/>
-      <c r="CG13" s="399"/>
-      <c r="CH13" s="346"/>
-      <c r="CI13" s="346"/>
+      <c r="J13" s="390"/>
+      <c r="K13" s="390"/>
+      <c r="L13" s="390"/>
+      <c r="M13" s="390"/>
+      <c r="N13" s="390"/>
+      <c r="O13" s="390"/>
+      <c r="P13" s="390"/>
+      <c r="Q13" s="390"/>
+      <c r="R13" s="390"/>
+      <c r="S13" s="390"/>
+      <c r="T13" s="390"/>
+      <c r="U13" s="390"/>
+      <c r="V13" s="390"/>
+      <c r="W13" s="390"/>
+      <c r="X13" s="390"/>
+      <c r="Y13" s="390"/>
+      <c r="Z13" s="390"/>
+      <c r="AA13" s="390"/>
+      <c r="AB13" s="390"/>
+      <c r="AC13" s="390"/>
+      <c r="AD13" s="390"/>
+      <c r="AE13" s="390"/>
+      <c r="AF13" s="390"/>
+      <c r="AG13" s="390"/>
+      <c r="AH13" s="390"/>
+      <c r="AI13" s="390"/>
+      <c r="AJ13" s="390"/>
+      <c r="AK13" s="390"/>
+      <c r="AL13" s="390"/>
+      <c r="AM13" s="390"/>
+      <c r="AN13" s="390"/>
+      <c r="AO13" s="390"/>
+      <c r="AP13" s="390"/>
+      <c r="AQ13" s="390"/>
+      <c r="AR13" s="390"/>
+      <c r="AS13" s="390"/>
+      <c r="AT13" s="390"/>
+      <c r="AU13" s="390"/>
+      <c r="AV13" s="390"/>
+      <c r="AW13" s="390"/>
+      <c r="AX13" s="390"/>
+      <c r="AY13" s="390"/>
+      <c r="AZ13" s="390"/>
+      <c r="BA13" s="390"/>
+      <c r="BB13" s="390"/>
+      <c r="BC13" s="390"/>
+      <c r="BD13" s="390"/>
+      <c r="BE13" s="390"/>
+      <c r="BF13" s="390"/>
+      <c r="BG13" s="390"/>
+      <c r="BH13" s="390"/>
+      <c r="BI13" s="390"/>
+      <c r="BJ13" s="390"/>
+      <c r="BK13" s="390"/>
+      <c r="BL13" s="390"/>
+      <c r="BM13" s="390"/>
+      <c r="BN13" s="390"/>
+      <c r="BO13" s="390"/>
+      <c r="BP13" s="390"/>
+      <c r="BQ13" s="390"/>
+      <c r="BR13" s="390"/>
+      <c r="BS13" s="390"/>
+      <c r="BT13" s="390"/>
+      <c r="BU13" s="391"/>
+      <c r="BV13" s="390"/>
+      <c r="BW13" s="390"/>
+      <c r="BX13" s="390"/>
+      <c r="BY13" s="390"/>
+      <c r="BZ13" s="390"/>
+      <c r="CA13" s="390"/>
+      <c r="CB13" s="390"/>
+      <c r="CE13" s="393"/>
+      <c r="CF13" s="346"/>
+      <c r="CG13" s="346"/>
     </row>
-    <row r="14" spans="1:87" s="360" customFormat="1" ht="21" customHeight="1">
+    <row r="14" spans="1:85" s="358" customFormat="1" ht="21" customHeight="1">
       <c r="A14" s="349"/>
       <c r="B14" s="354"/>
       <c r="C14" s="354"/>
@@ -16465,38 +16407,38 @@
         <v>170460000</v>
       </c>
       <c r="J14" s="354"/>
-      <c r="K14" s="413">
+      <c r="K14" s="406">
         <f>SUM(K15:K21)</f>
         <v>75.5</v>
       </c>
-      <c r="L14" s="413"/>
-      <c r="M14" s="413"/>
-      <c r="N14" s="413"/>
-      <c r="O14" s="413"/>
-      <c r="P14" s="413"/>
-      <c r="Q14" s="413"/>
-      <c r="R14" s="413">
+      <c r="L14" s="406"/>
+      <c r="M14" s="406"/>
+      <c r="N14" s="406"/>
+      <c r="O14" s="406"/>
+      <c r="P14" s="406"/>
+      <c r="Q14" s="406"/>
+      <c r="R14" s="406">
         <f>SUM(R15:R21)</f>
         <v>12</v>
       </c>
-      <c r="S14" s="413">
+      <c r="S14" s="406">
         <f>SUM(S15:S21)</f>
         <v>0</v>
       </c>
-      <c r="T14" s="413"/>
-      <c r="U14" s="413">
+      <c r="T14" s="406"/>
+      <c r="U14" s="406">
         <f>SUM(U15:U21)</f>
         <v>0</v>
       </c>
-      <c r="V14" s="413">
+      <c r="V14" s="406">
         <f>SUM(V15:V21)</f>
         <v>0</v>
       </c>
-      <c r="W14" s="413">
+      <c r="W14" s="406">
         <f>SUM(W15:W21)</f>
         <v>0</v>
       </c>
-      <c r="X14" s="413">
+      <c r="X14" s="406">
         <f>SUM(X15:X21)</f>
         <v>0</v>
       </c>
@@ -16629,247 +16571,240 @@
         <f>SUM(BT15:BT21)</f>
         <v>104321384.61538464</v>
       </c>
-      <c r="BU14" s="414">
-        <f>SUM(BU15:BU21)</f>
-        <v>0</v>
-      </c>
-      <c r="BV14" s="358"/>
-      <c r="BW14" s="347"/>
+      <c r="BU14" s="347"/>
+      <c r="BV14" s="348"/>
+      <c r="BW14" s="348"/>
       <c r="BX14" s="348"/>
       <c r="BY14" s="348"/>
       <c r="BZ14" s="348"/>
       <c r="CA14" s="348"/>
       <c r="CB14" s="348"/>
-      <c r="CC14" s="348"/>
-      <c r="CD14" s="348"/>
     </row>
-    <row r="15" spans="1:87" s="360" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A15" s="465">
+    <row r="15" spans="1:85" s="358" customFormat="1" ht="30.5" customHeight="1">
+      <c r="A15" s="456">
         <f>IF(B15=0,"",COUNTA($B$15:(B15)))</f>
         <v>1</v>
       </c>
-      <c r="B15" s="466">
+      <c r="B15" s="457">
         <v>2405236</v>
       </c>
-      <c r="C15" s="467" t="s">
+      <c r="C15" s="458" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="468" t="s">
+      <c r="D15" s="459" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="469" t="s">
+      <c r="E15" s="460" t="s">
         <v>113</v>
       </c>
-      <c r="F15" s="469" t="s">
+      <c r="F15" s="460" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="470">
+      <c r="G15" s="461">
         <v>9520000</v>
       </c>
-      <c r="H15" s="470">
-        <f t="shared" ref="H15:H21" si="4">+IF(OR(CC15="ĐT PCCC",CC15="ĐP PCCC"),780000,IF(CC15="AT-VSV",300000,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="470">
-        <f t="shared" ref="I15:I21" si="5">CB15-BZ15-G15-H15</f>
+      <c r="H15" s="461">
+        <f t="shared" ref="H15:H21" si="4">+IF(OR(CA15="ĐT PCCC",CA15="ĐP PCCC"),780000,IF(CA15="AT-VSV",300000,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="461">
+        <f>BZ15-BX15-G15-H15</f>
         <v>50480000</v>
       </c>
-      <c r="J15" s="471">
+      <c r="J15" s="462">
         <v>1</v>
       </c>
-      <c r="K15" s="472">
+      <c r="K15" s="463">
         <v>11</v>
       </c>
-      <c r="L15" s="472"/>
-      <c r="M15" s="472"/>
-      <c r="N15" s="472"/>
-      <c r="O15" s="472">
+      <c r="L15" s="463"/>
+      <c r="M15" s="463"/>
+      <c r="N15" s="463"/>
+      <c r="O15" s="463">
         <v>2</v>
       </c>
-      <c r="P15" s="472"/>
-      <c r="Q15" s="472"/>
-      <c r="R15" s="472">
-        <v>0</v>
-      </c>
-      <c r="S15" s="472">
-        <v>0</v>
-      </c>
-      <c r="T15" s="472"/>
-      <c r="U15" s="472">
-        <v>0</v>
-      </c>
-      <c r="V15" s="472">
-        <v>0</v>
-      </c>
-      <c r="W15" s="472">
-        <v>0</v>
-      </c>
-      <c r="X15" s="472">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="470">
-        <f t="shared" ref="Y15:Y21" si="6">G15*(K15+L15)/26</f>
+      <c r="P15" s="463"/>
+      <c r="Q15" s="463"/>
+      <c r="R15" s="463">
+        <v>0</v>
+      </c>
+      <c r="S15" s="463">
+        <v>0</v>
+      </c>
+      <c r="T15" s="463"/>
+      <c r="U15" s="463">
+        <v>0</v>
+      </c>
+      <c r="V15" s="463">
+        <v>0</v>
+      </c>
+      <c r="W15" s="463">
+        <v>0</v>
+      </c>
+      <c r="X15" s="463">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="461">
+        <f t="shared" ref="Y15:Y21" si="5">G15*(K15+L15)/26</f>
         <v>4027692.3076923075</v>
       </c>
-      <c r="Z15" s="470">
-        <f t="shared" ref="Z15:Z21" si="7">M15*G15/26</f>
-        <v>0</v>
-      </c>
-      <c r="AA15" s="470">
-        <f t="shared" ref="AA15:AA21" si="8">G15*N15/26</f>
-        <v>0</v>
-      </c>
-      <c r="AB15" s="470">
-        <f t="shared" ref="AB15:AB21" si="9">G15*O15/26</f>
+      <c r="Z15" s="461">
+        <f t="shared" ref="Z15:Z21" si="6">M15*G15/26</f>
+        <v>0</v>
+      </c>
+      <c r="AA15" s="461">
+        <f t="shared" ref="AA15:AA21" si="7">G15*N15/26</f>
+        <v>0</v>
+      </c>
+      <c r="AB15" s="461">
+        <f t="shared" ref="AB15:AB21" si="8">G15*O15/26</f>
         <v>732307.69230769225</v>
       </c>
-      <c r="AC15" s="470">
-        <f t="shared" ref="AC15:AC21" si="10">G15*P15*150%/26</f>
-        <v>0</v>
-      </c>
-      <c r="AD15" s="470">
-        <f t="shared" ref="AD15:AD21" si="11">G15*Q15/26*200%</f>
-        <v>0</v>
-      </c>
-      <c r="AE15" s="470">
-        <f t="shared" ref="AE15:AE21" si="12">G15*R15/26*300%</f>
-        <v>0</v>
-      </c>
-      <c r="AF15" s="470">
-        <f t="shared" ref="AF15:AF21" si="13">IF(F15="LT",0,(G15+H15)/26*S15*30%)</f>
-        <v>0</v>
-      </c>
-      <c r="AG15" s="470">
-        <f t="shared" ref="AG15:AG21" si="14">T15*G15/23/8</f>
-        <v>0</v>
-      </c>
-      <c r="AH15" s="470">
-        <f t="shared" ref="AH15:AH21" si="15">CB15/26*U15</f>
-        <v>0</v>
-      </c>
-      <c r="AI15" s="470">
-        <f t="shared" ref="AI15:AI21" si="16">G15*V15/26</f>
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="470"/>
-      <c r="AK15" s="470">
-        <f t="shared" ref="AK15:AK21" si="17">BZ15*L15/26</f>
-        <v>0</v>
-      </c>
-      <c r="AL15" s="470"/>
-      <c r="AM15" s="470">
-        <f t="shared" ref="AM15:AM21" si="18">X15*CD15</f>
-        <v>0</v>
-      </c>
-      <c r="AN15" s="470">
+      <c r="AC15" s="461">
+        <f t="shared" ref="AC15:AC21" si="9">G15*P15*150%/26</f>
+        <v>0</v>
+      </c>
+      <c r="AD15" s="461">
+        <f t="shared" ref="AD15:AD21" si="10">G15*Q15/26*200%</f>
+        <v>0</v>
+      </c>
+      <c r="AE15" s="461">
+        <f t="shared" ref="AE15:AE21" si="11">G15*R15/26*300%</f>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="461">
+        <f t="shared" ref="AF15:AF21" si="12">IF(F15="LT",0,(G15+H15)/26*S15*30%)</f>
+        <v>0</v>
+      </c>
+      <c r="AG15" s="461">
+        <f t="shared" ref="AG15:AG21" si="13">T15*G15/23/8</f>
+        <v>0</v>
+      </c>
+      <c r="AH15" s="461">
+        <f>BZ15/26*U15</f>
+        <v>0</v>
+      </c>
+      <c r="AI15" s="461">
+        <f t="shared" ref="AI15:AI21" si="14">G15*V15/26</f>
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="461"/>
+      <c r="AK15" s="461">
+        <f>BX15*L15/26</f>
+        <v>0</v>
+      </c>
+      <c r="AL15" s="461"/>
+      <c r="AM15" s="461">
+        <f>X15*CB15</f>
+        <v>0</v>
+      </c>
+      <c r="AN15" s="461">
         <f>H15/26*(K15+L15)</f>
         <v>0</v>
       </c>
-      <c r="AO15" s="470">
-        <f>IF(F15="LN",I15*(K15+L15)/26+(H15+I15)*50%*M15/26+IF(F15="LT",BW15*O15/26-AB15,0)+MAX($G15*P15/26*150%,P15*$BW15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BW15/26)-AD15+MAX($G15*R15/26*300%,R15*$BW15/26)-AE15+BW15*S15/26-AF15+AH15-AG15,I15-I15*($CE$11-K15-L15)/26+(H15+I15)*50%*M15/26+IF(F15="LT",BW15*O15/26-AB15,0)+MAX($G15*P15/26*150%,P15*$BW15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BW15/26)-AD15+MAX($G15*R15/26*300%,R15*$BW15/26)-AE15+BW15*S15/26-AF15+AH15-AG15+(G15-G15*($CE$11-K15-L15)/26-Y15)+(H15-H15*($CE$11-K15-L15)/26-AN15))</f>
+      <c r="AO15" s="461">
+        <f>IF(F15="LN",I15*(K15+L15)/26+(H15+I15)*50%*M15/26+IF(F15="LT",BU15*O15/26-AB15,0)+MAX($G15*P15/26*150%,P15*$BU15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BU15/26)-AD15+MAX($G15*R15/26*300%,R15*$BU15/26)-AE15+BU15*S15/26-AF15+AH15-AG15,I15-I15*($CC$11-K15-L15)/26+(H15+I15)*50%*M15/26+IF(F15="LT",BU15*O15/26-AB15,0)+MAX($G15*P15/26*150%,P15*$BU15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BU15/26)-AD15+MAX($G15*R15/26*300%,R15*$BU15/26)-AE15+BU15*S15/26-AF15+AH15-AG15+(G15-G15*($CC$11-K15-L15)/26-Y15)+(H15-H15*($CC$11-K15-L15)/26-AN15))</f>
         <v>27547692.307692312</v>
       </c>
-      <c r="AP15" s="470"/>
-      <c r="AQ15" s="470"/>
-      <c r="AR15" s="470"/>
-      <c r="AS15" s="470"/>
-      <c r="AT15" s="470"/>
-      <c r="AU15" s="470"/>
-      <c r="AV15" s="470">
-        <f t="shared" ref="AV15:AV21" si="19">Y15+Z15+AA15+AB15+AC15+AD15+AE15+AF15+AG15+AI15+AJ15+AK15+AL15+AM15+AN15+AO15+AP15-AQ15+AR15+AS15+AT15+AU15</f>
+      <c r="AP15" s="461"/>
+      <c r="AQ15" s="461"/>
+      <c r="AR15" s="461"/>
+      <c r="AS15" s="461"/>
+      <c r="AT15" s="461"/>
+      <c r="AU15" s="461"/>
+      <c r="AV15" s="461">
+        <f t="shared" ref="AV15:AV21" si="15">Y15+Z15+AA15+AB15+AC15+AD15+AE15+AF15+AG15+AI15+AJ15+AK15+AL15+AM15+AN15+AO15+AP15-AQ15+AR15+AS15+AT15+AU15</f>
         <v>32307692.307692312</v>
       </c>
-      <c r="AW15" s="470"/>
-      <c r="AX15" s="470" t="s">
+      <c r="AW15" s="461"/>
+      <c r="AX15" s="461" t="s">
         <v>101</v>
       </c>
-      <c r="AY15" s="473">
-        <f t="shared" ref="AY15:BA21" si="20">ROUND(IF($AX15="x",($G15+$H15)*AY$11,0),0)</f>
+      <c r="AY15" s="464">
+        <f t="shared" ref="AY15:BA21" si="16">ROUND(IF($AX15="x",($G15+$H15)*AY$11,0),0)</f>
         <v>761600</v>
       </c>
-      <c r="AZ15" s="473">
-        <f t="shared" si="20"/>
+      <c r="AZ15" s="464">
+        <f t="shared" si="16"/>
         <v>142800</v>
       </c>
-      <c r="BA15" s="473">
-        <f t="shared" si="20"/>
+      <c r="BA15" s="464">
+        <f t="shared" si="16"/>
         <v>95200</v>
       </c>
-      <c r="BB15" s="473">
-        <f t="shared" ref="BB15:BB21" si="21">SUM(AY15:BA15)</f>
+      <c r="BB15" s="464">
+        <f t="shared" ref="BB15:BB21" si="17">SUM(AY15:BA15)</f>
         <v>999600</v>
       </c>
-      <c r="BC15" s="473"/>
-      <c r="BD15" s="473"/>
-      <c r="BE15" s="473">
-        <f t="shared" ref="BE15:BE21" si="22">IF(G15*1%&gt;=234000,234000,G15*1%)</f>
+      <c r="BC15" s="464"/>
+      <c r="BD15" s="464"/>
+      <c r="BE15" s="464">
+        <f t="shared" ref="BE15:BE21" si="18">IF(G15*1%&gt;=234000,234000,G15*1%)</f>
         <v>95200</v>
       </c>
-      <c r="BF15" s="473">
-        <f t="shared" ref="BF15:BF21" si="23">AM15+IF(AR15&gt;="730000",730000,AR15)+IF(((AV15-AM15-IF(AR15&gt;="730000",730000,AR15)-AS15)*15%-AS15)&gt;"0",((AV15-AM15-IF(AR15&gt;="730000",730000,AR15)-AS15)*15%-AS15),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG15" s="473">
-        <f t="shared" ref="BG15:BG21" si="24">AV15-BF15+AW15</f>
+      <c r="BF15" s="464">
+        <f t="shared" ref="BF15:BF21" si="19">AM15+IF(AR15&gt;="730000",730000,AR15)+IF(((AV15-AM15-IF(AR15&gt;="730000",730000,AR15)-AS15)*15%-AS15)&gt;"0",((AV15-AM15-IF(AR15&gt;="730000",730000,AR15)-AS15)*15%-AS15),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG15" s="464">
+        <f t="shared" ref="BG15:BG21" si="20">AV15-BF15+AW15</f>
         <v>32307692.307692312</v>
       </c>
-      <c r="BH15" s="473">
+      <c r="BH15" s="464">
         <v>3</v>
       </c>
-      <c r="BI15" s="473">
-        <f t="shared" ref="BI15:BI21" si="25">BG15-BB15-BC15+BD15-BH15*4400000-IF(E15="CT",11000000,0)</f>
+      <c r="BI15" s="464">
+        <f t="shared" ref="BI15:BI21" si="21">BG15-BB15-BC15+BD15-BH15*4400000-IF(E15="CT",11000000,0)</f>
         <v>18108092.307692312</v>
       </c>
-      <c r="BJ15" s="474">
-        <f t="shared" ref="BJ15:BJ21" si="26">IF(BI15&gt;0,ROUND(IF(BI15&gt;=80000000,BI15*35%-9850000,IF(BI15&gt;=52000000,BI15*30%-5850000,IF(BI15&gt;=32000000,BI15*25%-3250000,IF(BI15&gt;=18000000,BI15*20%-1650000,IF(BI15&gt;=10000000,BI15*15%-750000,IF(BI15&gt;5000000,BI15*10%-250000,BI15*5%)))))),0),0)</f>
+      <c r="BJ15" s="465">
+        <f t="shared" ref="BJ15:BJ21" si="22">IF(BI15&gt;0,ROUND(IF(BI15&gt;=80000000,BI15*35%-9850000,IF(BI15&gt;=52000000,BI15*30%-5850000,IF(BI15&gt;=32000000,BI15*25%-3250000,IF(BI15&gt;=18000000,BI15*20%-1650000,IF(BI15&gt;=10000000,BI15*15%-750000,IF(BI15&gt;5000000,BI15*10%-250000,BI15*5%)))))),0),0)</f>
         <v>1971618</v>
       </c>
-      <c r="BK15" s="473"/>
-      <c r="BL15" s="473"/>
-      <c r="BM15" s="473">
-        <v>0</v>
-      </c>
-      <c r="BN15" s="473"/>
-      <c r="BO15" s="473"/>
-      <c r="BP15" s="473"/>
-      <c r="BQ15" s="473"/>
-      <c r="BR15" s="473"/>
-      <c r="BS15" s="473" t="str">
-        <f t="shared" ref="BS15:BS21" si="27">IF(AV15&gt;=11000000,"80%","100%")</f>
+      <c r="BK15" s="464"/>
+      <c r="BL15" s="464"/>
+      <c r="BM15" s="464">
+        <v>0</v>
+      </c>
+      <c r="BN15" s="464"/>
+      <c r="BO15" s="464"/>
+      <c r="BP15" s="464"/>
+      <c r="BQ15" s="464"/>
+      <c r="BR15" s="464"/>
+      <c r="BS15" s="464" t="str">
+        <f t="shared" ref="BS15:BS21" si="23">IF(AV15&gt;=11000000,"80%","100%")</f>
         <v>80%</v>
       </c>
-      <c r="BT15" s="473">
-        <f t="shared" ref="BT15:BT21" si="28">AV15*BS15-BN15-BK15-BP15-BO15</f>
+      <c r="BT15" s="464">
+        <f t="shared" ref="BT15:BT21" si="24">AV15*BS15-BN15-BK15-BP15-BO15</f>
         <v>25846153.846153852</v>
       </c>
-      <c r="BU15" s="357"/>
-      <c r="BV15" s="358"/>
-      <c r="BW15" s="504">
+      <c r="BU15" s="495">
         <v>60000000</v>
       </c>
-      <c r="BX15" s="474">
-        <v>0</v>
-      </c>
-      <c r="BY15" s="474"/>
-      <c r="BZ15" s="474"/>
-      <c r="CA15" s="474">
-        <v>0</v>
-      </c>
-      <c r="CB15" s="474">
-        <f t="shared" ref="CB15:CB21" si="29">SUM(BW15:CA15)</f>
+      <c r="BV15" s="465">
+        <v>0</v>
+      </c>
+      <c r="BW15" s="465"/>
+      <c r="BX15" s="465"/>
+      <c r="BY15" s="465">
+        <v>0</v>
+      </c>
+      <c r="BZ15" s="465">
+        <f t="shared" ref="BZ15:BZ21" si="25">SUM(BU15:BY15)</f>
         <v>60000000</v>
       </c>
-      <c r="CC15" s="474" t="s">
+      <c r="CA15" s="465" t="s">
         <v>122</v>
       </c>
-      <c r="CD15" s="474"/>
-      <c r="CE15" s="416"/>
-      <c r="CF15" s="417"/>
-      <c r="CG15" s="417"/>
-      <c r="CH15" s="359"/>
-      <c r="CI15" s="359"/>
+      <c r="CB15" s="465"/>
+      <c r="CC15" s="408"/>
+      <c r="CD15" s="409"/>
+      <c r="CE15" s="409"/>
+      <c r="CF15" s="357"/>
+      <c r="CG15" s="357"/>
     </row>
-    <row r="16" spans="1:87" s="360" customFormat="1" ht="30.5" customHeight="1">
+    <row r="16" spans="1:85" s="358" customFormat="1" ht="30.5" customHeight="1">
       <c r="A16" s="349">
         <f>IF(B16=0,"",COUNTA($B$15:(B16)))</f>
         <v>2</v>
@@ -16897,10 +16832,10 @@
         <v>0</v>
       </c>
       <c r="I16" s="354">
-        <f t="shared" si="5"/>
+        <f>BZ16-BX16-G16-H16</f>
         <v>33520000</v>
       </c>
-      <c r="J16" s="415">
+      <c r="J16" s="407">
         <v>1</v>
       </c>
       <c r="K16" s="355">
@@ -16936,65 +16871,65 @@
         <v>0</v>
       </c>
       <c r="Y16" s="354">
+        <f t="shared" si="5"/>
+        <v>3424615.3846153845</v>
+      </c>
+      <c r="Z16" s="354">
         <f t="shared" si="6"/>
-        <v>3424615.3846153845</v>
-      </c>
-      <c r="Z16" s="354">
+        <v>163076.92307692306</v>
+      </c>
+      <c r="AA16" s="354">
         <f t="shared" si="7"/>
-        <v>163076.92307692306</v>
-      </c>
-      <c r="AA16" s="354">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="354">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AB16" s="354">
+        <v>652307.69230769225</v>
+      </c>
+      <c r="AC16" s="354">
         <f t="shared" si="9"/>
-        <v>652307.69230769225</v>
-      </c>
-      <c r="AC16" s="354">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="354">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AD16" s="354">
+      <c r="AE16" s="354">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AE16" s="354">
+      <c r="AF16" s="354">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AF16" s="354">
+      <c r="AG16" s="354">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AG16" s="354">
+      <c r="AH16" s="354">
+        <f>BZ16/26*U16</f>
+        <v>0</v>
+      </c>
+      <c r="AI16" s="354">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AH16" s="354">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AI16" s="354">
-        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ16" s="354"/>
       <c r="AK16" s="354">
-        <f t="shared" si="17"/>
+        <f>BX16*L16/26</f>
         <v>0</v>
       </c>
       <c r="AL16" s="354"/>
       <c r="AM16" s="354">
-        <f t="shared" si="18"/>
+        <f>X16*CB16</f>
         <v>0</v>
       </c>
       <c r="AN16" s="354">
-        <f t="shared" ref="AN16:AN21" si="30">H16/26*K16</f>
+        <f t="shared" ref="AN16:AN21" si="26">H16/26*K16</f>
         <v>0</v>
       </c>
       <c r="AO16" s="354">
-        <f>IF(F16="LN",I16*(K16+L16)/26+(H16+I16)*50%*M16/26+IF(F16="LT",BW16*O16/26-AB16,0)+MAX($G16*P16/26*150%,P16*$BW16/26)-AC16+MAX($G16*Q16/26*200%,Q16*$BW16/26)-AD16+MAX($G16*R16/26*300%,R16*$BW16/26)-AE16+BW16*S16/26-AF16+AH16-AG16,I16-I16*($CE$11-K16-L16)/26+(H16+I16)*50%*M16/26+IF(F16="LT",BW16*O16/26-AB16,0)+MAX($G16*P16/26*150%,P16*$BW16/26)-AC16+MAX($G16*Q16/26*200%,Q16*$BW16/26)-AD16+MAX($G16*R16/26*300%,R16*$BW16/26)-AE16+BW16*S16/26-AF16+AH16-AG16+(G16-G16*($CE$11-K16-L16)/26-Y16)+(H16-H16*($CE$11-K16-L16)/26-AN16))</f>
+        <f>IF(F16="LN",I16*(K16+L16)/26+(H16+I16)*50%*M16/26+IF(F16="LT",BU16*O16/26-AB16,0)+MAX($G16*P16/26*150%,P16*$BU16/26)-AC16+MAX($G16*Q16/26*200%,Q16*$BU16/26)-AD16+MAX($G16*R16/26*300%,R16*$BU16/26)-AE16+BU16*S16/26-AF16+AH16-AG16,I16-I16*($CC$11-K16-L16)/26+(H16+I16)*50%*M16/26+IF(F16="LT",BU16*O16/26-AB16,0)+MAX($G16*P16/26*150%,P16*$BU16/26)-AC16+MAX($G16*Q16/26*200%,Q16*$BU16/26)-AD16+MAX($G16*R16/26*300%,R16*$BU16/26)-AE16+BU16*S16/26-AF16+AH16-AG16+(G16-G16*($CC$11-K16-L16)/26-Y16)+(H16-H16*($CC$11-K16-L16)/26-AN16))</f>
         <v>17899230.769230772</v>
       </c>
       <c r="AP16" s="354"/>
@@ -17004,7 +16939,7 @@
       <c r="AT16" s="354"/>
       <c r="AU16" s="354"/>
       <c r="AV16" s="354">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>22139230.769230772</v>
       </c>
       <c r="AW16" s="354"/>
@@ -17012,42 +16947,42 @@
         <v>101</v>
       </c>
       <c r="AY16" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>678400</v>
       </c>
       <c r="AZ16" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>127200</v>
       </c>
       <c r="BA16" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>84800</v>
       </c>
       <c r="BB16" s="356">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>890400</v>
       </c>
       <c r="BC16" s="356"/>
       <c r="BD16" s="356"/>
       <c r="BE16" s="356">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>84800</v>
       </c>
       <c r="BF16" s="356">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BG16" s="356">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>22139230.769230772</v>
       </c>
       <c r="BH16" s="356"/>
       <c r="BI16" s="356">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>10248830.769230772</v>
       </c>
       <c r="BJ16" s="348">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v>787325</v>
       </c>
       <c r="BK16" s="356"/>
@@ -17061,49 +16996,47 @@
       <c r="BQ16" s="356"/>
       <c r="BR16" s="356"/>
       <c r="BS16" s="356" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>80%</v>
       </c>
       <c r="BT16" s="356">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>17711384.61538462</v>
       </c>
-      <c r="BU16" s="357"/>
-      <c r="BV16" s="358"/>
-      <c r="BW16" s="347">
+      <c r="BU16" s="347">
         <v>40000000</v>
       </c>
-      <c r="BX16" s="348">
-        <v>0</v>
-      </c>
+      <c r="BV16" s="348">
+        <v>0</v>
+      </c>
+      <c r="BW16" s="348">
+        <v>0</v>
+      </c>
+      <c r="BX16" s="348"/>
       <c r="BY16" s="348">
-        <v>0</v>
-      </c>
-      <c r="BZ16" s="348"/>
-      <c r="CA16" s="348">
-        <f t="shared" ref="CA16:CA21" si="31">+BW16*5%</f>
+        <f t="shared" ref="BY16:BY21" si="27">+BU16*5%</f>
         <v>2000000</v>
       </c>
-      <c r="CB16" s="348">
-        <f t="shared" si="29"/>
+      <c r="BZ16" s="348">
+        <f t="shared" si="25"/>
         <v>42000000</v>
       </c>
-      <c r="CC16" s="348" t="s">
+      <c r="CA16" s="348" t="s">
         <v>114</v>
       </c>
-      <c r="CD16" s="348"/>
-      <c r="CE16" s="416"/>
-      <c r="CF16" s="417"/>
-      <c r="CG16" s="417"/>
-      <c r="CH16" s="359"/>
-      <c r="CI16" s="359"/>
+      <c r="CB16" s="348"/>
+      <c r="CC16" s="408"/>
+      <c r="CD16" s="409"/>
+      <c r="CE16" s="409"/>
+      <c r="CF16" s="357"/>
+      <c r="CG16" s="357"/>
     </row>
-    <row r="17" spans="1:87" s="360" customFormat="1" ht="30.5" customHeight="1">
+    <row r="17" spans="1:85" s="358" customFormat="1" ht="30.5" customHeight="1">
       <c r="A17" s="349">
         <f>IF(B17=0,"",COUNTA($B$15:(B17)))</f>
         <v>3</v>
       </c>
-      <c r="B17" s="361" t="s">
+      <c r="B17" s="359" t="s">
         <v>104</v>
       </c>
       <c r="C17" s="351" t="s">
@@ -17126,10 +17059,10 @@
         <v>300000</v>
       </c>
       <c r="I17" s="354">
-        <f t="shared" si="5"/>
+        <f>BZ17-BX17-G17-H17</f>
         <v>33880000</v>
       </c>
-      <c r="J17" s="415">
+      <c r="J17" s="407">
         <v>1</v>
       </c>
       <c r="K17" s="355">
@@ -17163,65 +17096,65 @@
         <v>0</v>
       </c>
       <c r="Y17" s="354">
+        <f t="shared" si="5"/>
+        <v>3308461.5384615385</v>
+      </c>
+      <c r="Z17" s="354">
         <f t="shared" si="6"/>
-        <v>3308461.5384615385</v>
-      </c>
-      <c r="Z17" s="354">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="354">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AA17" s="354">
+      <c r="AB17" s="354">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AB17" s="354">
+        <v>601538.4615384615</v>
+      </c>
+      <c r="AC17" s="354">
         <f t="shared" si="9"/>
-        <v>601538.4615384615</v>
-      </c>
-      <c r="AC17" s="354">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="354">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AD17" s="354">
+      <c r="AE17" s="354">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AE17" s="354">
+        <v>3609230.769230769</v>
+      </c>
+      <c r="AF17" s="354">
         <f t="shared" si="12"/>
-        <v>3609230.769230769</v>
-      </c>
-      <c r="AF17" s="354">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="354">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AG17" s="354">
+      <c r="AH17" s="354">
+        <f>BZ17/26*U17</f>
+        <v>0</v>
+      </c>
+      <c r="AI17" s="354">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AH17" s="354">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AI17" s="354">
-        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ17" s="354"/>
       <c r="AK17" s="354">
-        <f t="shared" si="17"/>
+        <f>BX17*L17/26</f>
         <v>0</v>
       </c>
       <c r="AL17" s="354"/>
       <c r="AM17" s="354">
-        <f t="shared" si="18"/>
+        <f>X17*CB17</f>
         <v>0</v>
       </c>
       <c r="AN17" s="354">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>126923.07692307694</v>
       </c>
       <c r="AO17" s="354">
-        <f>IF(F17="LN",I17*(K17+L17)/26+(H17+I17)*50%*M17/26+IF(F17="LT",BW17*O17/26-AB17,0)+MAX($G17*P17/26*150%,P17*$BW17/26)-AC17+MAX($G17*Q17/26*200%,Q17*$BW17/26)-AD17+MAX($G17*R17/26*300%,R17*$BW17/26)-AE17+BW17*S17/26-AF17+AH17-AG17,I17-I17*($CE$11-K17-L17)/26+(H17+I17)*50%*M17/26+IF(F17="LT",BW17*O17/26-AB17,0)+MAX($G17*P17/26*150%,P17*$BW17/26)-AC17+MAX($G17*Q17/26*200%,Q17*$BW17/26)-AD17+MAX($G17*R17/26*300%,R17*$BW17/26)-AE17+BW17*S17/26-AF17+AH17-AG17+(G17-G17*($CE$11-K17-L17)/26-Y17)+(H17-H17*($CE$11-K17-L17)/26-AN17))</f>
+        <f>IF(F17="LN",I17*(K17+L17)/26+(H17+I17)*50%*M17/26+IF(F17="LT",BU17*O17/26-AB17,0)+MAX($G17*P17/26*150%,P17*$BU17/26)-AC17+MAX($G17*Q17/26*200%,Q17*$BU17/26)-AD17+MAX($G17*R17/26*300%,R17*$BU17/26)-AE17+BU17*S17/26-AF17+AH17-AG17,I17-I17*($CC$11-K17-L17)/26+(H17+I17)*50%*M17/26+IF(F17="LT",BU17*O17/26-AB17,0)+MAX($G17*P17/26*150%,P17*$BU17/26)-AC17+MAX($G17*Q17/26*200%,Q17*$BU17/26)-AD17+MAX($G17*R17/26*300%,R17*$BU17/26)-AE17+BU17*S17/26-AF17+AH17-AG17+(G17-G17*($CC$11-K17-L17)/26-Y17)+(H17-H17*($CC$11-K17-L17)/26-AN17))</f>
         <v>20969230.769230772</v>
       </c>
       <c r="AP17" s="354"/>
@@ -17231,7 +17164,7 @@
       <c r="AT17" s="354"/>
       <c r="AU17" s="354"/>
       <c r="AV17" s="354">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>28615384.615384616</v>
       </c>
       <c r="AW17" s="354"/>
@@ -17239,42 +17172,42 @@
         <v>101</v>
       </c>
       <c r="AY17" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>649600</v>
       </c>
       <c r="AZ17" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>121800</v>
       </c>
       <c r="BA17" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>81200</v>
       </c>
       <c r="BB17" s="356">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>852600</v>
       </c>
       <c r="BC17" s="356"/>
       <c r="BD17" s="356"/>
       <c r="BE17" s="356">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>78200</v>
       </c>
       <c r="BF17" s="356">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BG17" s="356">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>28615384.615384616</v>
       </c>
       <c r="BH17" s="356"/>
       <c r="BI17" s="356">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>16762784.615384616</v>
       </c>
       <c r="BJ17" s="348">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v>1764418</v>
       </c>
       <c r="BK17" s="356"/>
@@ -17288,44 +17221,42 @@
       <c r="BQ17" s="356"/>
       <c r="BR17" s="356"/>
       <c r="BS17" s="356" t="str">
+        <f t="shared" si="23"/>
+        <v>80%</v>
+      </c>
+      <c r="BT17" s="356">
+        <f t="shared" si="24"/>
+        <v>22892307.692307696</v>
+      </c>
+      <c r="BU17" s="347">
+        <v>40000000</v>
+      </c>
+      <c r="BV17" s="348">
+        <v>0</v>
+      </c>
+      <c r="BW17" s="348">
+        <v>0</v>
+      </c>
+      <c r="BX17" s="348"/>
+      <c r="BY17" s="348">
         <f t="shared" si="27"/>
-        <v>80%</v>
-      </c>
-      <c r="BT17" s="356">
-        <f t="shared" si="28"/>
-        <v>22892307.692307696</v>
-      </c>
-      <c r="BU17" s="357"/>
-      <c r="BV17" s="358"/>
-      <c r="BW17" s="347">
-        <v>40000000</v>
-      </c>
-      <c r="BX17" s="348">
-        <v>0</v>
-      </c>
-      <c r="BY17" s="348">
-        <v>0</v>
-      </c>
-      <c r="BZ17" s="348"/>
-      <c r="CA17" s="348">
-        <f t="shared" si="31"/>
         <v>2000000</v>
       </c>
-      <c r="CB17" s="348">
-        <f t="shared" si="29"/>
+      <c r="BZ17" s="348">
+        <f t="shared" si="25"/>
         <v>42000000</v>
       </c>
-      <c r="CC17" s="348" t="s">
+      <c r="CA17" s="348" t="s">
         <v>118</v>
       </c>
-      <c r="CD17" s="348"/>
-      <c r="CE17" s="416"/>
-      <c r="CF17" s="417"/>
-      <c r="CG17" s="417"/>
-      <c r="CH17" s="359"/>
-      <c r="CI17" s="359"/>
+      <c r="CB17" s="348"/>
+      <c r="CC17" s="408"/>
+      <c r="CD17" s="409"/>
+      <c r="CE17" s="409"/>
+      <c r="CF17" s="357"/>
+      <c r="CG17" s="357"/>
     </row>
-    <row r="18" spans="1:87" s="360" customFormat="1" ht="30.5" customHeight="1">
+    <row r="18" spans="1:85" s="358" customFormat="1" ht="30.5" customHeight="1">
       <c r="A18" s="349">
         <f>IF(B18=0,"",COUNTA($B$15:(B18)))</f>
         <v>4</v>
@@ -17353,10 +17284,10 @@
         <v>0</v>
       </c>
       <c r="I18" s="354">
-        <f t="shared" si="5"/>
+        <f>BZ18-BX18-G18-H18</f>
         <v>17160000</v>
       </c>
-      <c r="J18" s="415">
+      <c r="J18" s="407">
         <v>1</v>
       </c>
       <c r="K18" s="355">
@@ -17392,65 +17323,65 @@
         <v>0</v>
       </c>
       <c r="Y18" s="354">
+        <f t="shared" si="5"/>
+        <v>2822884.6153846155</v>
+      </c>
+      <c r="Z18" s="354">
         <f t="shared" si="6"/>
-        <v>2822884.6153846155</v>
-      </c>
-      <c r="Z18" s="354">
+        <v>134423.07692307694</v>
+      </c>
+      <c r="AA18" s="354">
         <f t="shared" si="7"/>
-        <v>134423.07692307694</v>
-      </c>
-      <c r="AA18" s="354">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="354">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AB18" s="354">
+        <v>537692.30769230775</v>
+      </c>
+      <c r="AC18" s="354">
         <f t="shared" si="9"/>
-        <v>537692.30769230775</v>
-      </c>
-      <c r="AC18" s="354">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="354">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AD18" s="354">
+      <c r="AE18" s="354">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AE18" s="354">
+      <c r="AF18" s="354">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AF18" s="354">
+      <c r="AG18" s="354">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AG18" s="354">
+      <c r="AH18" s="354">
+        <f>BZ18/26*U18</f>
+        <v>0</v>
+      </c>
+      <c r="AI18" s="354">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AH18" s="354">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AI18" s="354">
-        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ18" s="354"/>
       <c r="AK18" s="354">
-        <f t="shared" si="17"/>
+        <f>BX18*L18/26</f>
         <v>0</v>
       </c>
       <c r="AL18" s="354"/>
       <c r="AM18" s="354">
-        <f t="shared" si="18"/>
+        <f>X18*CB18</f>
         <v>0</v>
       </c>
       <c r="AN18" s="354">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AO18" s="354">
-        <f>IF(F18="LN",I18*(K18+L18)/26+(H18+I18)*50%*M18/26+IF(F18="LT",BW18*O18/26-AB18,0)+MAX($G18*P18/26*150%,P18*$BW18/26)-AC18+MAX($G18*Q18/26*200%,Q18*$BW18/26)-AD18+MAX($G18*R18/26*300%,R18*$BW18/26)-AE18+BW18*S18/26-AF18+AH18-AG18,I18-I18*($CE$11-K18-L18)/26+(H18+I18)*50%*M18/26+IF(F18="LT",BW18*O18/26-AB18,0)+MAX($G18*P18/26*150%,P18*$BW18/26)-AC18+MAX($G18*Q18/26*200%,Q18*$BW18/26)-AD18+MAX($G18*R18/26*300%,R18*$BW18/26)-AE18+BW18*S18/26-AF18+AH18-AG18+(G18-G18*($CE$11-K18-L18)/26-Y18)+(H18-H18*($CE$11-K18-L18)/26-AN18))</f>
+        <f>IF(F18="LN",I18*(K18+L18)/26+(H18+I18)*50%*M18/26+IF(F18="LT",BU18*O18/26-AB18,0)+MAX($G18*P18/26*150%,P18*$BU18/26)-AC18+MAX($G18*Q18/26*200%,Q18*$BU18/26)-AD18+MAX($G18*R18/26*300%,R18*$BU18/26)-AE18+BU18*S18/26-AF18+AH18-AG18,I18-I18*($CC$11-K18-L18)/26+(H18+I18)*50%*M18/26+IF(F18="LT",BU18*O18/26-AB18,0)+MAX($G18*P18/26*150%,P18*$BU18/26)-AC18+MAX($G18*Q18/26*200%,Q18*$BU18/26)-AD18+MAX($G18*R18/26*300%,R18*$BU18/26)-AE18+BU18*S18/26-AF18+AH18-AG18+(G18-G18*($CC$11-K18-L18)/26-Y18)+(H18-H18*($CC$11-K18-L18)/26-AN18))</f>
         <v>9255384.615384616</v>
       </c>
       <c r="AP18" s="354"/>
@@ -17460,7 +17391,7 @@
       <c r="AT18" s="354"/>
       <c r="AU18" s="354"/>
       <c r="AV18" s="354">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>12750384.615384616</v>
       </c>
       <c r="AW18" s="354"/>
@@ -17468,42 +17399,42 @@
         <v>101</v>
       </c>
       <c r="AY18" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>559200</v>
       </c>
       <c r="AZ18" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>104850</v>
       </c>
       <c r="BA18" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>69900</v>
       </c>
       <c r="BB18" s="356">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>733950</v>
       </c>
       <c r="BC18" s="356"/>
       <c r="BD18" s="356"/>
       <c r="BE18" s="356">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>69900</v>
       </c>
       <c r="BF18" s="356">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BG18" s="356">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>12750384.615384616</v>
       </c>
       <c r="BH18" s="356"/>
       <c r="BI18" s="356">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>1016434.615384616</v>
       </c>
       <c r="BJ18" s="348">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v>50822</v>
       </c>
       <c r="BK18" s="356"/>
@@ -17517,49 +17448,47 @@
       <c r="BQ18" s="356"/>
       <c r="BR18" s="356"/>
       <c r="BS18" s="356" t="str">
+        <f t="shared" si="23"/>
+        <v>80%</v>
+      </c>
+      <c r="BT18" s="356">
+        <f t="shared" si="24"/>
+        <v>10200307.692307694</v>
+      </c>
+      <c r="BU18" s="347">
+        <v>23000000</v>
+      </c>
+      <c r="BV18" s="348">
+        <v>0</v>
+      </c>
+      <c r="BW18" s="348">
+        <v>0</v>
+      </c>
+      <c r="BX18" s="348"/>
+      <c r="BY18" s="348">
         <f t="shared" si="27"/>
-        <v>80%</v>
-      </c>
-      <c r="BT18" s="356">
-        <f t="shared" si="28"/>
-        <v>10200307.692307694</v>
-      </c>
-      <c r="BU18" s="357"/>
-      <c r="BV18" s="358"/>
-      <c r="BW18" s="347">
-        <v>23000000</v>
-      </c>
-      <c r="BX18" s="348">
-        <v>0</v>
-      </c>
-      <c r="BY18" s="348">
-        <v>0</v>
-      </c>
-      <c r="BZ18" s="348"/>
-      <c r="CA18" s="348">
-        <f t="shared" si="31"/>
         <v>1150000</v>
       </c>
-      <c r="CB18" s="348">
-        <f t="shared" si="29"/>
+      <c r="BZ18" s="348">
+        <f t="shared" si="25"/>
         <v>24150000</v>
       </c>
-      <c r="CC18" s="348" t="s">
+      <c r="CA18" s="348" t="s">
         <v>114</v>
       </c>
-      <c r="CD18" s="348"/>
-      <c r="CE18" s="416"/>
-      <c r="CF18" s="417"/>
-      <c r="CG18" s="417"/>
-      <c r="CH18" s="359"/>
-      <c r="CI18" s="359"/>
+      <c r="CB18" s="348"/>
+      <c r="CC18" s="408"/>
+      <c r="CD18" s="409"/>
+      <c r="CE18" s="409"/>
+      <c r="CF18" s="357"/>
+      <c r="CG18" s="357"/>
     </row>
-    <row r="19" spans="1:87" s="360" customFormat="1" ht="30.5" customHeight="1">
+    <row r="19" spans="1:85" s="358" customFormat="1" ht="30.5" customHeight="1">
       <c r="A19" s="349">
         <f>IF(B19=0,"",COUNTA($B$15:(B19)))</f>
         <v>5</v>
       </c>
-      <c r="B19" s="361" t="s">
+      <c r="B19" s="359" t="s">
         <v>108</v>
       </c>
       <c r="C19" s="351" t="s">
@@ -17582,10 +17511,10 @@
         <v>300000</v>
       </c>
       <c r="I19" s="354">
-        <f t="shared" si="5"/>
+        <f>BZ19-BX19-G19-H19</f>
         <v>6400000</v>
       </c>
-      <c r="J19" s="415">
+      <c r="J19" s="407">
         <v>1</v>
       </c>
       <c r="K19" s="355">
@@ -17619,65 +17548,65 @@
         <v>0</v>
       </c>
       <c r="Y19" s="354">
+        <f t="shared" si="5"/>
+        <v>2051923.076923077</v>
+      </c>
+      <c r="Z19" s="354">
         <f t="shared" si="6"/>
-        <v>2051923.076923077</v>
-      </c>
-      <c r="Z19" s="354">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="354">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AA19" s="354">
+      <c r="AB19" s="354">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AB19" s="354">
+        <v>373076.92307692306</v>
+      </c>
+      <c r="AC19" s="354">
         <f t="shared" si="9"/>
-        <v>373076.92307692306</v>
-      </c>
-      <c r="AC19" s="354">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="354">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AD19" s="354">
+      <c r="AE19" s="354">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AE19" s="354">
+        <v>2238461.5384615385</v>
+      </c>
+      <c r="AF19" s="354">
         <f t="shared" si="12"/>
-        <v>2238461.5384615385</v>
-      </c>
-      <c r="AF19" s="354">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="354">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AG19" s="354">
+      <c r="AH19" s="354">
+        <f>BZ19/26*U19</f>
+        <v>0</v>
+      </c>
+      <c r="AI19" s="354">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AH19" s="354">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AI19" s="354">
-        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ19" s="354"/>
       <c r="AK19" s="354">
-        <f t="shared" si="17"/>
+        <f>BX19*L19/26</f>
         <v>0</v>
       </c>
       <c r="AL19" s="354"/>
       <c r="AM19" s="354">
-        <f t="shared" si="18"/>
+        <f>X19*CB19</f>
         <v>0</v>
       </c>
       <c r="AN19" s="354">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>126923.07692307694</v>
       </c>
       <c r="AO19" s="354">
-        <f>IF(F19="LN",I19*(K19+L19)/26+(H19+I19)*50%*M19/26+IF(F19="LT",BW19*O19/26-AB19,0)+MAX($G19*P19/26*150%,P19*$BW19/26)-AC19+MAX($G19*Q19/26*200%,Q19*$BW19/26)-AD19+MAX($G19*R19/26*300%,R19*$BW19/26)-AE19+BW19*S19/26-AF19+AH19-AG19,I19-I19*($CE$11-K19-L19)/26+(H19+I19)*50%*M19/26+IF(F19="LT",BW19*O19/26-AB19,0)+MAX($G19*P19/26*150%,P19*$BW19/26)-AC19+MAX($G19*Q19/26*200%,Q19*$BW19/26)-AD19+MAX($G19*R19/26*300%,R19*$BW19/26)-AE19+BW19*S19/26-AF19+AH19-AG19+(G19-G19*($CE$11-K19-L19)/26-Y19)+(H19-H19*($CE$11-K19-L19)/26-AN19))</f>
+        <f>IF(F19="LN",I19*(K19+L19)/26+(H19+I19)*50%*M19/26+IF(F19="LT",BU19*O19/26-AB19,0)+MAX($G19*P19/26*150%,P19*$BU19/26)-AC19+MAX($G19*Q19/26*200%,Q19*$BU19/26)-AD19+MAX($G19*R19/26*300%,R19*$BU19/26)-AE19+BU19*S19/26-AF19+AH19-AG19,I19-I19*($CC$11-K19-L19)/26+(H19+I19)*50%*M19/26+IF(F19="LT",BU19*O19/26-AB19,0)+MAX($G19*P19/26*150%,P19*$BU19/26)-AC19+MAX($G19*Q19/26*200%,Q19*$BU19/26)-AD19+MAX($G19*R19/26*300%,R19*$BU19/26)-AE19+BU19*S19/26-AF19+AH19-AG19+(G19-G19*($CC$11-K19-L19)/26-Y19)+(H19-H19*($CC$11-K19-L19)/26-AN19))</f>
         <v>2707692.3076923075</v>
       </c>
       <c r="AP19" s="354"/>
@@ -17687,7 +17616,7 @@
       <c r="AT19" s="354"/>
       <c r="AU19" s="354"/>
       <c r="AV19" s="354">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>7498076.9230769221</v>
       </c>
       <c r="AW19" s="354"/>
@@ -17695,42 +17624,42 @@
         <v>101</v>
       </c>
       <c r="AY19" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>412000</v>
       </c>
       <c r="AZ19" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>77250</v>
       </c>
       <c r="BA19" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>51500</v>
       </c>
       <c r="BB19" s="356">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>540750</v>
       </c>
       <c r="BC19" s="356"/>
       <c r="BD19" s="356"/>
       <c r="BE19" s="356">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>48500</v>
       </c>
       <c r="BF19" s="356">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BG19" s="356">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>7498076.9230769221</v>
       </c>
       <c r="BH19" s="356"/>
       <c r="BI19" s="356">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>-4042673.0769230779</v>
       </c>
       <c r="BJ19" s="348">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BK19" s="356"/>
@@ -17744,44 +17673,42 @@
       <c r="BQ19" s="356"/>
       <c r="BR19" s="356"/>
       <c r="BS19" s="356" t="str">
+        <f t="shared" si="23"/>
+        <v>100%</v>
+      </c>
+      <c r="BT19" s="356">
+        <f t="shared" si="24"/>
+        <v>7498076.9230769221</v>
+      </c>
+      <c r="BU19" s="347">
+        <v>11000000</v>
+      </c>
+      <c r="BV19" s="348">
+        <v>0</v>
+      </c>
+      <c r="BW19" s="348">
+        <v>0</v>
+      </c>
+      <c r="BX19" s="348"/>
+      <c r="BY19" s="348">
         <f t="shared" si="27"/>
-        <v>100%</v>
-      </c>
-      <c r="BT19" s="356">
-        <f t="shared" si="28"/>
-        <v>7498076.9230769221</v>
-      </c>
-      <c r="BU19" s="357"/>
-      <c r="BV19" s="358"/>
-      <c r="BW19" s="347">
-        <v>11000000</v>
-      </c>
-      <c r="BX19" s="348">
-        <v>0</v>
-      </c>
-      <c r="BY19" s="348">
-        <v>0</v>
-      </c>
-      <c r="BZ19" s="348"/>
-      <c r="CA19" s="348">
-        <f t="shared" si="31"/>
         <v>550000</v>
       </c>
-      <c r="CB19" s="348">
-        <f t="shared" si="29"/>
+      <c r="BZ19" s="348">
+        <f t="shared" si="25"/>
         <v>11550000</v>
       </c>
-      <c r="CC19" s="348" t="s">
+      <c r="CA19" s="348" t="s">
         <v>118</v>
       </c>
-      <c r="CD19" s="348"/>
-      <c r="CE19" s="416"/>
-      <c r="CF19" s="417"/>
-      <c r="CG19" s="417"/>
-      <c r="CH19" s="359"/>
-      <c r="CI19" s="359"/>
+      <c r="CB19" s="348"/>
+      <c r="CC19" s="408"/>
+      <c r="CD19" s="409"/>
+      <c r="CE19" s="409"/>
+      <c r="CF19" s="357"/>
+      <c r="CG19" s="357"/>
     </row>
-    <row r="20" spans="1:87" s="360" customFormat="1" ht="30.5" customHeight="1">
+    <row r="20" spans="1:85" s="358" customFormat="1" ht="30.5" customHeight="1">
       <c r="A20" s="349">
         <f>IF(B20=0,"",COUNTA($B$15:(B20)))</f>
         <v>6</v>
@@ -17809,10 +17736,10 @@
         <v>0</v>
       </c>
       <c r="I20" s="354">
-        <f t="shared" si="5"/>
+        <f>BZ20-BX20-G20-H20</f>
         <v>17810000</v>
       </c>
-      <c r="J20" s="415">
+      <c r="J20" s="407">
         <v>1</v>
       </c>
       <c r="K20" s="355">
@@ -17848,65 +17775,65 @@
         <v>0</v>
       </c>
       <c r="Y20" s="354">
+        <f t="shared" si="5"/>
+        <v>2560384.6153846155</v>
+      </c>
+      <c r="Z20" s="354">
         <f t="shared" si="6"/>
-        <v>2560384.6153846155</v>
-      </c>
-      <c r="Z20" s="354">
+        <v>121923.07692307692</v>
+      </c>
+      <c r="AA20" s="354">
         <f t="shared" si="7"/>
-        <v>121923.07692307692</v>
-      </c>
-      <c r="AA20" s="354">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="354">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AB20" s="354">
+        <v>487692.30769230769</v>
+      </c>
+      <c r="AC20" s="354">
         <f t="shared" si="9"/>
-        <v>487692.30769230769</v>
-      </c>
-      <c r="AC20" s="354">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="354">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AD20" s="354">
+      <c r="AE20" s="354">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AE20" s="354">
+      <c r="AF20" s="354">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AF20" s="354">
+      <c r="AG20" s="354">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AG20" s="354">
+      <c r="AH20" s="354">
+        <f>BZ20/26*U20</f>
+        <v>0</v>
+      </c>
+      <c r="AI20" s="354">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AH20" s="354">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AI20" s="354">
-        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ20" s="354"/>
       <c r="AK20" s="354">
-        <f t="shared" si="17"/>
+        <f>BX20*L20/26</f>
         <v>0</v>
       </c>
       <c r="AL20" s="354"/>
       <c r="AM20" s="354">
-        <f t="shared" si="18"/>
+        <f>X20*CB20</f>
         <v>0</v>
       </c>
       <c r="AN20" s="354">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AO20" s="354">
-        <f>IF(F20="LN",I20*(K20+L20)/26+(H20+I20)*50%*M20/26+IF(F20="LT",BW20*O20/26-AB20,0)+MAX($G20*P20/26*150%,P20*$BW20/26)-AC20+MAX($G20*Q20/26*200%,Q20*$BW20/26)-AD20+MAX($G20*R20/26*300%,R20*$BW20/26)-AE20+BW20*S20/26-AF20+AH20-AG20,I20-I20*($CE$11-K20-L20)/26+(H20+I20)*50%*M20/26+IF(F20="LT",BW20*O20/26-AB20,0)+MAX($G20*P20/26*150%,P20*$BW20/26)-AC20+MAX($G20*Q20/26*200%,Q20*$BW20/26)-AD20+MAX($G20*R20/26*300%,R20*$BW20/26)-AE20+BW20*S20/26-AF20+AH20-AG20+(G20-G20*($CE$11-K20-L20)/26-Y20)+(H20-H20*($CE$11-K20-L20)/26-AN20))</f>
+        <f>IF(F20="LN",I20*(K20+L20)/26+(H20+I20)*50%*M20/26+IF(F20="LT",BU20*O20/26-AB20,0)+MAX($G20*P20/26*150%,P20*$BU20/26)-AC20+MAX($G20*Q20/26*200%,Q20*$BU20/26)-AD20+MAX($G20*R20/26*300%,R20*$BU20/26)-AE20+BU20*S20/26-AF20+AH20-AG20,I20-I20*($CC$11-K20-L20)/26+(H20+I20)*50%*M20/26+IF(F20="LT",BU20*O20/26-AB20,0)+MAX($G20*P20/26*150%,P20*$BU20/26)-AC20+MAX($G20*Q20/26*200%,Q20*$BU20/26)-AD20+MAX($G20*R20/26*300%,R20*$BU20/26)-AE20+BU20*S20/26-AF20+AH20-AG20+(G20-G20*($CC$11-K20-L20)/26-Y20)+(H20-H20*($CC$11-K20-L20)/26-AN20))</f>
         <v>9574134.615384616</v>
       </c>
       <c r="AP20" s="354"/>
@@ -17916,7 +17843,7 @@
       <c r="AT20" s="354"/>
       <c r="AU20" s="354"/>
       <c r="AV20" s="354">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>12744134.615384616</v>
       </c>
       <c r="AW20" s="354"/>
@@ -17924,42 +17851,42 @@
         <v>101</v>
       </c>
       <c r="AY20" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>507200</v>
       </c>
       <c r="AZ20" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>95100</v>
       </c>
       <c r="BA20" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>63400</v>
       </c>
       <c r="BB20" s="356">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>665700</v>
       </c>
       <c r="BC20" s="356"/>
       <c r="BD20" s="356"/>
       <c r="BE20" s="356">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>63400</v>
       </c>
       <c r="BF20" s="356">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BG20" s="356">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>12744134.615384616</v>
       </c>
       <c r="BH20" s="356"/>
       <c r="BI20" s="356">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>1078434.615384616</v>
       </c>
       <c r="BJ20" s="348">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v>53922</v>
       </c>
       <c r="BK20" s="356"/>
@@ -17973,49 +17900,47 @@
       <c r="BQ20" s="356"/>
       <c r="BR20" s="356"/>
       <c r="BS20" s="356" t="str">
+        <f t="shared" si="23"/>
+        <v>80%</v>
+      </c>
+      <c r="BT20" s="356">
+        <f t="shared" si="24"/>
+        <v>10195307.692307694</v>
+      </c>
+      <c r="BU20" s="347">
+        <v>23000000</v>
+      </c>
+      <c r="BV20" s="348">
+        <v>0</v>
+      </c>
+      <c r="BW20" s="348">
+        <v>0</v>
+      </c>
+      <c r="BX20" s="348"/>
+      <c r="BY20" s="348">
         <f t="shared" si="27"/>
-        <v>80%</v>
-      </c>
-      <c r="BT20" s="356">
-        <f t="shared" si="28"/>
-        <v>10195307.692307694</v>
-      </c>
-      <c r="BU20" s="357"/>
-      <c r="BV20" s="358"/>
-      <c r="BW20" s="347">
-        <v>23000000</v>
-      </c>
-      <c r="BX20" s="348">
-        <v>0</v>
-      </c>
-      <c r="BY20" s="348">
-        <v>0</v>
-      </c>
-      <c r="BZ20" s="348"/>
-      <c r="CA20" s="348">
-        <f t="shared" si="31"/>
         <v>1150000</v>
       </c>
-      <c r="CB20" s="348">
-        <f t="shared" si="29"/>
+      <c r="BZ20" s="348">
+        <f t="shared" si="25"/>
         <v>24150000</v>
       </c>
-      <c r="CC20" s="348" t="s">
+      <c r="CA20" s="348" t="s">
         <v>114</v>
       </c>
-      <c r="CD20" s="348"/>
-      <c r="CE20" s="416"/>
-      <c r="CF20" s="417"/>
-      <c r="CG20" s="417"/>
-      <c r="CH20" s="359"/>
-      <c r="CI20" s="359"/>
+      <c r="CB20" s="348"/>
+      <c r="CC20" s="408"/>
+      <c r="CD20" s="409"/>
+      <c r="CE20" s="409"/>
+      <c r="CF20" s="357"/>
+      <c r="CG20" s="357"/>
     </row>
-    <row r="21" spans="1:87" s="360" customFormat="1" ht="30.5" customHeight="1">
+    <row r="21" spans="1:85" s="358" customFormat="1" ht="30.5" customHeight="1">
       <c r="A21" s="349">
         <f>IF(B21=0,"",COUNTA($B$15:(B21)))</f>
         <v>7</v>
       </c>
-      <c r="B21" s="361" t="s">
+      <c r="B21" s="359" t="s">
         <v>115</v>
       </c>
       <c r="C21" s="351" t="s">
@@ -18038,10 +17963,10 @@
         <v>300000</v>
       </c>
       <c r="I21" s="354">
-        <f t="shared" si="5"/>
+        <f>BZ21-BX21-G21-H21</f>
         <v>11210000</v>
       </c>
-      <c r="J21" s="415">
+      <c r="J21" s="407">
         <v>1</v>
       </c>
       <c r="K21" s="355">
@@ -18075,65 +18000,65 @@
         <v>0</v>
       </c>
       <c r="Y21" s="354">
+        <f t="shared" si="5"/>
+        <v>2682307.6923076925</v>
+      </c>
+      <c r="Z21" s="354">
         <f t="shared" si="6"/>
-        <v>2682307.6923076925</v>
-      </c>
-      <c r="Z21" s="354">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="354">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AA21" s="354">
+      <c r="AB21" s="354">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AB21" s="354">
+        <v>487692.30769230769</v>
+      </c>
+      <c r="AC21" s="354">
         <f t="shared" si="9"/>
-        <v>487692.30769230769</v>
-      </c>
-      <c r="AC21" s="354">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="354">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AD21" s="354">
+      <c r="AE21" s="354">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AE21" s="354">
+        <v>2926153.846153846</v>
+      </c>
+      <c r="AF21" s="354">
         <f t="shared" si="12"/>
-        <v>2926153.846153846</v>
-      </c>
-      <c r="AF21" s="354">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="354">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AG21" s="354">
+      <c r="AH21" s="354">
+        <f>BZ21/26*U21</f>
+        <v>0</v>
+      </c>
+      <c r="AI21" s="354">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AH21" s="354">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AI21" s="354">
-        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ21" s="354"/>
       <c r="AK21" s="354">
-        <f t="shared" si="17"/>
+        <f>BX21*L21/26</f>
         <v>0</v>
       </c>
       <c r="AL21" s="354"/>
       <c r="AM21" s="354">
-        <f t="shared" si="18"/>
+        <f>X21*CB21</f>
         <v>0</v>
       </c>
       <c r="AN21" s="354">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>126923.07692307694</v>
       </c>
       <c r="AO21" s="354">
-        <f>IF(F21="LN",I21*(K21+L21)/26+(H21+I21)*50%*M21/26+IF(F21="LT",BW21*O21/26-AB21,0)+MAX($G21*P21/26*150%,P21*$BW21/26)-AC21+MAX($G21*Q21/26*200%,Q21*$BW21/26)-AD21+MAX($G21*R21/26*300%,R21*$BW21/26)-AE21+BW21*S21/26-AF21+AH21-AG21,I21-I21*($CE$11-K21-L21)/26+(H21+I21)*50%*M21/26+IF(F21="LT",BW21*O21/26-AB21,0)+MAX($G21*P21/26*150%,P21*$BW21/26)-AC21+MAX($G21*Q21/26*200%,Q21*$BW21/26)-AD21+MAX($G21*R21/26*300%,R21*$BW21/26)-AE21+BW21*S21/26-AF21+AH21-AG21+(G21-G21*($CE$11-K21-L21)/26-Y21)+(H21-H21*($CE$11-K21-L21)/26-AN21))</f>
+        <f>IF(F21="LN",I21*(K21+L21)/26+(H21+I21)*50%*M21/26+IF(F21="LT",BU21*O21/26-AB21,0)+MAX($G21*P21/26*150%,P21*$BU21/26)-AC21+MAX($G21*Q21/26*200%,Q21*$BU21/26)-AD21+MAX($G21*R21/26*300%,R21*$BU21/26)-AE21+BU21*S21/26-AF21+AH21-AG21,I21-I21*($CC$11-K21-L21)/26+(H21+I21)*50%*M21/26+IF(F21="LT",BU21*O21/26-AB21,0)+MAX($G21*P21/26*150%,P21*$BU21/26)-AC21+MAX($G21*Q21/26*200%,Q21*$BU21/26)-AD21+MAX($G21*R21/26*300%,R21*$BU21/26)-AE21+BU21*S21/26-AF21+AH21-AG21+(G21-G21*($CC$11-K21-L21)/26-Y21)+(H21-H21*($CC$11-K21-L21)/26-AN21))</f>
         <v>6249230.7692307699</v>
       </c>
       <c r="AP21" s="354"/>
@@ -18143,7 +18068,7 @@
       <c r="AT21" s="354"/>
       <c r="AU21" s="354"/>
       <c r="AV21" s="354">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>12472307.692307692</v>
       </c>
       <c r="AW21" s="354"/>
@@ -18151,42 +18076,42 @@
         <v>101</v>
       </c>
       <c r="AY21" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>531200</v>
       </c>
       <c r="AZ21" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>99600</v>
       </c>
       <c r="BA21" s="356">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>66400</v>
       </c>
       <c r="BB21" s="356">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>697200</v>
       </c>
       <c r="BC21" s="356"/>
       <c r="BD21" s="356"/>
       <c r="BE21" s="356">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>63400</v>
       </c>
       <c r="BF21" s="356">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BG21" s="356">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>12472307.692307692</v>
       </c>
       <c r="BH21" s="356"/>
       <c r="BI21" s="356">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>775107.69230769202</v>
       </c>
       <c r="BJ21" s="348">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v>38755</v>
       </c>
       <c r="BK21" s="356"/>
@@ -18200,191 +18125,185 @@
       <c r="BQ21" s="356"/>
       <c r="BR21" s="356"/>
       <c r="BS21" s="356" t="str">
+        <f t="shared" si="23"/>
+        <v>80%</v>
+      </c>
+      <c r="BT21" s="356">
+        <f t="shared" si="24"/>
+        <v>9977846.153846154</v>
+      </c>
+      <c r="BU21" s="347">
+        <v>17000000</v>
+      </c>
+      <c r="BV21" s="348">
+        <v>0</v>
+      </c>
+      <c r="BW21" s="348">
+        <v>0</v>
+      </c>
+      <c r="BX21" s="348"/>
+      <c r="BY21" s="348">
         <f t="shared" si="27"/>
-        <v>80%</v>
-      </c>
-      <c r="BT21" s="356">
-        <f t="shared" si="28"/>
-        <v>9977846.153846154</v>
-      </c>
-      <c r="BU21" s="357"/>
-      <c r="BV21" s="358"/>
-      <c r="BW21" s="347">
-        <v>17000000</v>
-      </c>
-      <c r="BX21" s="348">
-        <v>0</v>
-      </c>
-      <c r="BY21" s="348">
-        <v>0</v>
-      </c>
-      <c r="BZ21" s="348"/>
-      <c r="CA21" s="348">
-        <f t="shared" si="31"/>
         <v>850000</v>
       </c>
-      <c r="CB21" s="348">
-        <f t="shared" si="29"/>
+      <c r="BZ21" s="348">
+        <f t="shared" si="25"/>
         <v>17850000</v>
       </c>
-      <c r="CC21" s="348" t="s">
+      <c r="CA21" s="348" t="s">
         <v>118</v>
       </c>
-      <c r="CD21" s="348"/>
-      <c r="CE21" s="416"/>
-      <c r="CF21" s="417"/>
-      <c r="CG21" s="417"/>
-      <c r="CH21" s="359"/>
-      <c r="CI21" s="359"/>
+      <c r="CB21" s="348"/>
+      <c r="CC21" s="408"/>
+      <c r="CD21" s="409"/>
+      <c r="CE21" s="409"/>
+      <c r="CF21" s="357"/>
+      <c r="CG21" s="357"/>
     </row>
-    <row r="22" spans="1:87" s="418" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B22" s="419"/>
-      <c r="I22" s="420"/>
-      <c r="J22" s="420"/>
-      <c r="K22" s="421"/>
-      <c r="L22" s="421"/>
-      <c r="M22" s="421"/>
-      <c r="N22" s="421"/>
-      <c r="O22" s="421"/>
-      <c r="P22" s="421"/>
-      <c r="Q22" s="421"/>
-      <c r="R22" s="421"/>
-      <c r="S22" s="421"/>
-      <c r="T22" s="421"/>
-      <c r="U22" s="422"/>
-      <c r="V22" s="422"/>
-      <c r="W22" s="423"/>
-      <c r="X22" s="423"/>
-      <c r="AC22" s="424"/>
-      <c r="BJ22" s="425"/>
-      <c r="BN22" s="425"/>
-      <c r="BO22" s="425"/>
-      <c r="BP22" s="425"/>
-      <c r="BQ22" s="425"/>
-      <c r="BR22" s="425"/>
-      <c r="BS22" s="425"/>
-      <c r="BT22" s="425"/>
-      <c r="BU22" s="425"/>
-      <c r="BV22" s="426"/>
-      <c r="BW22" s="427"/>
-      <c r="BX22" s="427"/>
-      <c r="BY22" s="427"/>
-      <c r="BZ22" s="427"/>
-      <c r="CA22" s="427"/>
-      <c r="CF22" s="428"/>
+    <row r="22" spans="1:85" s="410" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B22" s="411"/>
+      <c r="I22" s="412"/>
+      <c r="J22" s="412"/>
+      <c r="K22" s="413"/>
+      <c r="L22" s="413"/>
+      <c r="M22" s="413"/>
+      <c r="N22" s="413"/>
+      <c r="O22" s="413"/>
+      <c r="P22" s="413"/>
+      <c r="Q22" s="413"/>
+      <c r="R22" s="413"/>
+      <c r="S22" s="413"/>
+      <c r="T22" s="413"/>
+      <c r="U22" s="414"/>
+      <c r="V22" s="414"/>
+      <c r="W22" s="415"/>
+      <c r="X22" s="415"/>
+      <c r="AC22" s="416"/>
+      <c r="BJ22" s="417"/>
+      <c r="BN22" s="417"/>
+      <c r="BO22" s="417"/>
+      <c r="BP22" s="417"/>
+      <c r="BQ22" s="417"/>
+      <c r="BR22" s="417"/>
+      <c r="BS22" s="417"/>
+      <c r="BT22" s="417"/>
+      <c r="BU22" s="418"/>
+      <c r="BV22" s="418"/>
+      <c r="BW22" s="418"/>
+      <c r="BX22" s="418"/>
+      <c r="BY22" s="418"/>
+      <c r="CD22" s="419"/>
     </row>
-    <row r="23" spans="1:87" s="429" customFormat="1" ht="21" customHeight="1">
-      <c r="B23" s="430"/>
-      <c r="C23" s="430"/>
-      <c r="D23" s="430"/>
-      <c r="E23" s="430"/>
-      <c r="F23" s="430"/>
-      <c r="G23" s="430"/>
-      <c r="H23" s="430"/>
-      <c r="I23" s="430"/>
-      <c r="J23" s="431"/>
-      <c r="K23" s="432"/>
-      <c r="L23" s="432"/>
-      <c r="M23" s="432"/>
-      <c r="N23" s="432"/>
-      <c r="O23" s="432"/>
-      <c r="P23" s="432"/>
-      <c r="Q23" s="432"/>
-      <c r="U23" s="433"/>
-      <c r="V23" s="432"/>
-      <c r="W23" s="430"/>
-      <c r="X23" s="430"/>
-      <c r="Y23" s="430"/>
-      <c r="Z23" s="430"/>
-      <c r="AA23" s="430"/>
-      <c r="AB23" s="430"/>
-      <c r="AC23" s="430"/>
-      <c r="AK23" s="430"/>
-      <c r="AM23" s="430"/>
-      <c r="AN23" s="430"/>
-      <c r="AO23" s="430"/>
-      <c r="AP23" s="430"/>
-      <c r="AQ23" s="430"/>
-      <c r="AR23" s="430"/>
-      <c r="AS23" s="430"/>
-      <c r="AT23" s="430"/>
-      <c r="AU23" s="430"/>
-      <c r="AV23" s="430"/>
-      <c r="AW23" s="430"/>
-      <c r="AX23" s="430"/>
-      <c r="BC23" s="434"/>
-      <c r="BD23" s="434"/>
-      <c r="BJ23" s="430"/>
-      <c r="BL23" s="430"/>
-      <c r="BM23" s="430"/>
-      <c r="BN23" s="430" t="s">
+    <row r="23" spans="1:85" s="420" customFormat="1" ht="21" customHeight="1">
+      <c r="B23" s="421"/>
+      <c r="C23" s="421"/>
+      <c r="D23" s="421"/>
+      <c r="E23" s="421"/>
+      <c r="F23" s="421"/>
+      <c r="G23" s="421"/>
+      <c r="H23" s="421"/>
+      <c r="I23" s="421"/>
+      <c r="J23" s="422"/>
+      <c r="K23" s="423"/>
+      <c r="L23" s="423"/>
+      <c r="M23" s="423"/>
+      <c r="N23" s="423"/>
+      <c r="O23" s="423"/>
+      <c r="P23" s="423"/>
+      <c r="Q23" s="423"/>
+      <c r="U23" s="424"/>
+      <c r="V23" s="423"/>
+      <c r="W23" s="421"/>
+      <c r="X23" s="421"/>
+      <c r="Y23" s="421"/>
+      <c r="Z23" s="421"/>
+      <c r="AA23" s="421"/>
+      <c r="AB23" s="421"/>
+      <c r="AC23" s="421"/>
+      <c r="AK23" s="421"/>
+      <c r="AM23" s="421"/>
+      <c r="AN23" s="421"/>
+      <c r="AO23" s="421"/>
+      <c r="AP23" s="421"/>
+      <c r="AQ23" s="421"/>
+      <c r="AR23" s="421"/>
+      <c r="AS23" s="421"/>
+      <c r="AT23" s="421"/>
+      <c r="AU23" s="421"/>
+      <c r="AV23" s="421"/>
+      <c r="AW23" s="421"/>
+      <c r="AX23" s="421"/>
+      <c r="BC23" s="425"/>
+      <c r="BD23" s="425"/>
+      <c r="BJ23" s="421"/>
+      <c r="BL23" s="421"/>
+      <c r="BM23" s="421"/>
+      <c r="BN23" s="421" t="s">
         <v>119</v>
       </c>
-      <c r="BO23" s="430"/>
-      <c r="BP23" s="430"/>
-      <c r="BQ23" s="430"/>
-      <c r="BR23" s="430"/>
-      <c r="BS23" s="430"/>
-      <c r="BT23" s="430"/>
-      <c r="BU23" s="430"/>
-      <c r="BV23" s="430"/>
-      <c r="BW23" s="435"/>
-      <c r="BX23" s="435"/>
-      <c r="BY23" s="435"/>
-      <c r="BZ23" s="435"/>
-      <c r="CA23" s="435"/>
+      <c r="BO23" s="421"/>
+      <c r="BP23" s="421"/>
+      <c r="BQ23" s="421"/>
+      <c r="BR23" s="421"/>
+      <c r="BS23" s="421"/>
+      <c r="BT23" s="421"/>
+      <c r="BU23" s="426"/>
+      <c r="BV23" s="426"/>
+      <c r="BW23" s="426"/>
+      <c r="BX23" s="426"/>
+      <c r="BY23" s="426"/>
     </row>
-    <row r="24" spans="1:87" s="429" customFormat="1" ht="18" customHeight="1">
-      <c r="B24" s="436"/>
-      <c r="I24" s="431"/>
-      <c r="J24" s="431"/>
-      <c r="K24" s="433"/>
-      <c r="L24" s="433"/>
-      <c r="M24" s="433"/>
-      <c r="N24" s="433"/>
-      <c r="O24" s="433"/>
-      <c r="P24" s="433"/>
-      <c r="Q24" s="433"/>
-      <c r="R24" s="432"/>
-      <c r="U24" s="433"/>
-      <c r="V24" s="433"/>
-      <c r="W24" s="437"/>
-      <c r="X24" s="437"/>
-      <c r="AN24" s="435"/>
-      <c r="AV24" s="430"/>
-      <c r="AW24" s="430"/>
-      <c r="AX24" s="430"/>
-      <c r="AY24" s="435"/>
-      <c r="AZ24" s="435"/>
-      <c r="BA24" s="435"/>
-      <c r="BB24" s="435"/>
-      <c r="BL24" s="430"/>
-      <c r="BM24" s="434"/>
-      <c r="BW24" s="435"/>
-      <c r="BX24" s="435"/>
-      <c r="BY24" s="435"/>
-      <c r="BZ24" s="435"/>
-      <c r="CA24" s="435"/>
-      <c r="CF24" s="438"/>
+    <row r="24" spans="1:85" s="420" customFormat="1" ht="18" customHeight="1">
+      <c r="B24" s="427"/>
+      <c r="I24" s="422"/>
+      <c r="J24" s="422"/>
+      <c r="K24" s="424"/>
+      <c r="L24" s="424"/>
+      <c r="M24" s="424"/>
+      <c r="N24" s="424"/>
+      <c r="O24" s="424"/>
+      <c r="P24" s="424"/>
+      <c r="Q24" s="424"/>
+      <c r="R24" s="423"/>
+      <c r="U24" s="424"/>
+      <c r="V24" s="424"/>
+      <c r="W24" s="428"/>
+      <c r="X24" s="428"/>
+      <c r="AN24" s="426"/>
+      <c r="AV24" s="421"/>
+      <c r="AW24" s="421"/>
+      <c r="AX24" s="421"/>
+      <c r="AY24" s="426"/>
+      <c r="AZ24" s="426"/>
+      <c r="BA24" s="426"/>
+      <c r="BB24" s="426"/>
+      <c r="BL24" s="421"/>
+      <c r="BM24" s="425"/>
+      <c r="BU24" s="426"/>
+      <c r="BV24" s="426"/>
+      <c r="BW24" s="426"/>
+      <c r="BX24" s="426"/>
+      <c r="BY24" s="426"/>
+      <c r="CD24" s="429"/>
     </row>
-    <row r="25" spans="1:87" ht="15" customHeight="1">
-      <c r="D25" s="442" t="s">
+    <row r="25" spans="1:85" ht="15" customHeight="1">
+      <c r="D25" s="433" t="s">
         <v>152</v>
       </c>
-      <c r="I25" s="443"/>
-      <c r="X25" s="365"/>
-      <c r="BZ25" s="365" t="s">
+      <c r="I25" s="434"/>
+      <c r="X25" s="363"/>
+      <c r="BX25" s="363" t="s">
         <v>147</v>
       </c>
-      <c r="CF25" s="447"/>
+      <c r="CD25" s="438"/>
     </row>
-    <row r="26" spans="1:87" ht="73.5" customHeight="1">
-      <c r="J26" s="364"/>
-      <c r="X26" s="365"/>
+    <row r="26" spans="1:85" ht="73.5" customHeight="1">
+      <c r="J26" s="362"/>
+      <c r="X26" s="363"/>
     </row>
   </sheetData>
-  <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <mergeCells count="82">
+  <autoFilter ref="A12:CG21" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <mergeCells count="81">
     <mergeCell ref="L9:L11"/>
     <mergeCell ref="N9:N11"/>
     <mergeCell ref="BG10:BG11"/>
@@ -18397,9 +18316,9 @@
     <mergeCell ref="AV8:AV11"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="BX8:CA10"/>
+    <mergeCell ref="BV8:BY10"/>
     <mergeCell ref="C8:C11"/>
-    <mergeCell ref="BW8:BW11"/>
+    <mergeCell ref="BU8:BU11"/>
     <mergeCell ref="AI9:AI11"/>
     <mergeCell ref="BQ8:BR8"/>
     <mergeCell ref="D8:D11"/>
@@ -18412,7 +18331,7 @@
     <mergeCell ref="AP8:AP11"/>
     <mergeCell ref="AR8:AR11"/>
     <mergeCell ref="F8:F11"/>
-    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="BZ8:BZ11"/>
     <mergeCell ref="AJ9:AJ11"/>
     <mergeCell ref="AL9:AL11"/>
     <mergeCell ref="AN9:AN11"/>
@@ -18427,11 +18346,11 @@
     <mergeCell ref="AY8:BP8"/>
     <mergeCell ref="AF9:AF11"/>
     <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="BU3:BZ6"/>
     <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="CA8:CA11"/>
     <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="A3:BT3"/>
     <mergeCell ref="AE9:AE11"/>
     <mergeCell ref="AO9:AO11"/>
     <mergeCell ref="B8:B11"/>
@@ -18447,7 +18366,6 @@
     <mergeCell ref="G8:G11"/>
     <mergeCell ref="BS8:BS11"/>
     <mergeCell ref="BK9:BP9"/>
-    <mergeCell ref="BU8:BU11"/>
     <mergeCell ref="R9:R11"/>
     <mergeCell ref="BR9:BR11"/>
     <mergeCell ref="BM10:BM11"/>
@@ -18459,7 +18377,7 @@
     <mergeCell ref="H8:H11"/>
     <mergeCell ref="J8:J11"/>
     <mergeCell ref="V9:W10"/>
-    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="CB8:CB11"/>
     <mergeCell ref="Y9:Y11"/>
     <mergeCell ref="AA9:AA11"/>
     <mergeCell ref="AK9:AK11"/>
@@ -18468,19 +18386,19 @@
     <mergeCell ref="Y8:AO8"/>
     <mergeCell ref="BJ10:BJ11"/>
   </mergeCells>
-  <conditionalFormatting sqref="B1:B12 B22:B1048576 C12:BU12">
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B12 B22:B1048576 C12:CD12 D13:F13 J13:BI13 BK13:CD13">
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B15:B21">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ13">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B12 B22:B1048576 C12:BT12">
+    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B12 B22:B1048576 C12:CB12 D13:F13 J13:BI13 BK13:CB13">
+    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.21" bottom="0.17" header="0.196850393700787" footer="0.196850393700787"/>
@@ -21479,19 +21397,19 @@
     <mergeCell ref="AK6:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BI10 BK10:BU10 BW9:CD10">
-    <cfRule type="duplicateValues" dxfId="6" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ10">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.21" bottom="0.17" header="0.196850393700787" footer="0.196850393700787"/>

--- a/thaco/color/1_Office_color Mid Cycle.xlsx
+++ b/thaco/color/1_Office_color Mid Cycle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8508E364-75E8-B94D-BB23-30761D63FF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D942B5-2E9B-B144-9EF0-6CAB76282C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38480" yWindow="500" windowWidth="38360" windowHeight="20700" tabRatio="761" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14874,7 +14874,7 @@
   <cols>
     <col min="1" max="1" width="5.5" style="430" customWidth="1"/>
     <col min="2" max="2" width="8.5" style="431" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="432" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" style="432" customWidth="1"/>
     <col min="4" max="4" width="5.5" style="360" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="5" max="5" width="5.5" style="360" customWidth="1" outlineLevel="1"/>
     <col min="6" max="6" width="5.5" style="361" bestFit="1" customWidth="1" outlineLevel="1"/>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="I14" s="354">
         <f>SUM(I15:I21)</f>
-        <v>170460000</v>
+        <v>173460000</v>
       </c>
       <c r="J14" s="354"/>
       <c r="K14" s="406">
@@ -16496,7 +16496,7 @@
       </c>
       <c r="AO14" s="354">
         <f t="shared" si="3"/>
-        <v>94202596.15384616</v>
+        <v>95587211.538461551</v>
       </c>
       <c r="AP14" s="354"/>
       <c r="AQ14" s="354"/>
@@ -16506,7 +16506,7 @@
       <c r="AU14" s="354"/>
       <c r="AV14" s="354">
         <f>SUM(AV15:AV21)</f>
-        <v>128527211.53846155</v>
+        <v>129911826.92307691</v>
       </c>
       <c r="AW14" s="354"/>
       <c r="AX14" s="354"/>
@@ -16541,7 +16541,7 @@
       <c r="BI14" s="354"/>
       <c r="BJ14" s="354">
         <f>SUM(BJ15:BJ21)</f>
-        <v>4666860</v>
+        <v>2979196</v>
       </c>
       <c r="BK14" s="354">
         <f>SUM(BK15:BK21)</f>
@@ -16569,7 +16569,7 @@
       <c r="BS14" s="354"/>
       <c r="BT14" s="354">
         <f>SUM(BT15:BT21)</f>
-        <v>104321384.61538464</v>
+        <v>105429076.92307696</v>
       </c>
       <c r="BU14" s="347"/>
       <c r="BV14" s="348"/>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="I15" s="461">
         <f>BZ15-BX15-G15-H15</f>
-        <v>50480000</v>
+        <v>53480000</v>
       </c>
       <c r="J15" s="462">
         <v>1</v>
@@ -16704,7 +16704,7 @@
       </c>
       <c r="AO15" s="461">
         <f>IF(F15="LN",I15*(K15+L15)/26+(H15+I15)*50%*M15/26+IF(F15="LT",BU15*O15/26-AB15,0)+MAX($G15*P15/26*150%,P15*$BU15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BU15/26)-AD15+MAX($G15*R15/26*300%,R15*$BU15/26)-AE15+BU15*S15/26-AF15+AH15-AG15,I15-I15*($CC$11-K15-L15)/26+(H15+I15)*50%*M15/26+IF(F15="LT",BU15*O15/26-AB15,0)+MAX($G15*P15/26*150%,P15*$BU15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BU15/26)-AD15+MAX($G15*R15/26*300%,R15*$BU15/26)-AE15+BU15*S15/26-AF15+AH15-AG15+(G15-G15*($CC$11-K15-L15)/26-Y15)+(H15-H15*($CC$11-K15-L15)/26-AN15))</f>
-        <v>27547692.307692312</v>
+        <v>28932307.692307696</v>
       </c>
       <c r="AP15" s="461"/>
       <c r="AQ15" s="461"/>
@@ -16714,7 +16714,7 @@
       <c r="AU15" s="461"/>
       <c r="AV15" s="461">
         <f t="shared" ref="AV15:AV21" si="15">Y15+Z15+AA15+AB15+AC15+AD15+AE15+AF15+AG15+AI15+AJ15+AK15+AL15+AM15+AN15+AO15+AP15-AQ15+AR15+AS15+AT15+AU15</f>
-        <v>32307692.307692312</v>
+        <v>33692307.692307696</v>
       </c>
       <c r="AW15" s="461"/>
       <c r="AX15" s="461" t="s">
@@ -16743,23 +16743,23 @@
         <v>95200</v>
       </c>
       <c r="BF15" s="464">
-        <f t="shared" ref="BF15:BF21" si="19">AM15+IF(AR15&gt;="730000",730000,AR15)+IF(((AV15-AM15-IF(AR15&gt;="730000",730000,AR15)-AS15)*15%-AS15)&gt;"0",((AV15-AM15-IF(AR15&gt;="730000",730000,AR15)-AS15)*15%-AS15),0)</f>
-        <v>0</v>
+        <f>AM15+IF(AR15&gt;=730000,730000,AR15)+IF(((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15)&gt;0,((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15),0)</f>
+        <v>5053846.153846154</v>
       </c>
       <c r="BG15" s="464">
-        <f t="shared" ref="BG15:BG21" si="20">AV15-BF15+AW15</f>
-        <v>32307692.307692312</v>
+        <f t="shared" ref="BG15:BG21" si="19">AV15-BF15+AW15</f>
+        <v>28638461.538461544</v>
       </c>
       <c r="BH15" s="464">
         <v>3</v>
       </c>
       <c r="BI15" s="464">
-        <f t="shared" ref="BI15:BI21" si="21">BG15-BB15-BC15+BD15-BH15*4400000-IF(E15="CT",11000000,0)</f>
-        <v>18108092.307692312</v>
+        <f t="shared" ref="BI15:BI21" si="20">BG15-BB15-BC15+BD15-BH15*4400000-IF(E15="CT",11000000,0)</f>
+        <v>14438861.538461544</v>
       </c>
       <c r="BJ15" s="465">
-        <f t="shared" ref="BJ15:BJ21" si="22">IF(BI15&gt;0,ROUND(IF(BI15&gt;=80000000,BI15*35%-9850000,IF(BI15&gt;=52000000,BI15*30%-5850000,IF(BI15&gt;=32000000,BI15*25%-3250000,IF(BI15&gt;=18000000,BI15*20%-1650000,IF(BI15&gt;=10000000,BI15*15%-750000,IF(BI15&gt;5000000,BI15*10%-250000,BI15*5%)))))),0),0)</f>
-        <v>1971618</v>
+        <f t="shared" ref="BJ15:BJ21" si="21">IF(BI15&gt;0,ROUND(IF(BI15&gt;=80000000,BI15*35%-9850000,IF(BI15&gt;=52000000,BI15*30%-5850000,IF(BI15&gt;=32000000,BI15*25%-3250000,IF(BI15&gt;=18000000,BI15*20%-1650000,IF(BI15&gt;=10000000,BI15*15%-750000,IF(BI15&gt;5000000,BI15*10%-250000,BI15*5%)))))),0),0)</f>
+        <v>1415829</v>
       </c>
       <c r="BK15" s="464"/>
       <c r="BL15" s="464"/>
@@ -16772,12 +16772,12 @@
       <c r="BQ15" s="464"/>
       <c r="BR15" s="464"/>
       <c r="BS15" s="464" t="str">
-        <f t="shared" ref="BS15:BS21" si="23">IF(AV15&gt;=11000000,"80%","100%")</f>
+        <f t="shared" ref="BS15:BS21" si="22">IF(AV15&gt;=11000000,"80%","100%")</f>
         <v>80%</v>
       </c>
       <c r="BT15" s="464">
-        <f t="shared" ref="BT15:BT21" si="24">AV15*BS15-BN15-BK15-BP15-BO15</f>
-        <v>25846153.846153852</v>
+        <f>AV15*BS15-BN15-BK15-BP15-BO15</f>
+        <v>26953846.15384616</v>
       </c>
       <c r="BU15" s="495">
         <v>60000000</v>
@@ -16788,11 +16788,12 @@
       <c r="BW15" s="465"/>
       <c r="BX15" s="465"/>
       <c r="BY15" s="465">
-        <v>0</v>
+        <f t="shared" ref="BY15:BY21" si="23">+BU15*5%</f>
+        <v>3000000</v>
       </c>
       <c r="BZ15" s="465">
-        <f t="shared" ref="BZ15:BZ21" si="25">SUM(BU15:BY15)</f>
-        <v>60000000</v>
+        <f t="shared" ref="BZ15:BZ21" si="24">SUM(BU15:BY15)</f>
+        <v>63000000</v>
       </c>
       <c r="CA15" s="465" t="s">
         <v>122</v>
@@ -16925,7 +16926,7 @@
         <v>0</v>
       </c>
       <c r="AN16" s="354">
-        <f t="shared" ref="AN16:AN21" si="26">H16/26*K16</f>
+        <f t="shared" ref="AN16:AN21" si="25">H16/26*K16</f>
         <v>0</v>
       </c>
       <c r="AO16" s="354">
@@ -16969,21 +16970,21 @@
         <v>84800</v>
       </c>
       <c r="BF16" s="356">
+        <f t="shared" ref="BF16:BF21" si="26">AM16+IF(AR16&gt;=730000,730000,AR16)+IF(((AV16-AM16-IF(AR16&gt;=730000,730000,AR16)-AS16)*15%-AS16)&gt;0,((AV16-AM16-IF(AR16&gt;=730000,730000,AR16)-AS16)*15%-AS16),0)</f>
+        <v>3320884.6153846155</v>
+      </c>
+      <c r="BG16" s="356">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BG16" s="356">
-        <f t="shared" si="20"/>
-        <v>22139230.769230772</v>
+        <v>18818346.153846156</v>
       </c>
       <c r="BH16" s="356"/>
       <c r="BI16" s="356">
+        <f t="shared" si="20"/>
+        <v>6927946.1538461559</v>
+      </c>
+      <c r="BJ16" s="348">
         <f t="shared" si="21"/>
-        <v>10248830.769230772</v>
-      </c>
-      <c r="BJ16" s="348">
-        <f t="shared" si="22"/>
-        <v>787325</v>
+        <v>442795</v>
       </c>
       <c r="BK16" s="356"/>
       <c r="BL16" s="356"/>
@@ -16996,11 +16997,11 @@
       <c r="BQ16" s="356"/>
       <c r="BR16" s="356"/>
       <c r="BS16" s="356" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>80%</v>
       </c>
       <c r="BT16" s="356">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="BT15:BT21" si="27">AV16*BS16-BN16-BK16-BP16-BO16</f>
         <v>17711384.61538462</v>
       </c>
       <c r="BU16" s="347">
@@ -17014,11 +17015,11 @@
       </c>
       <c r="BX16" s="348"/>
       <c r="BY16" s="348">
-        <f t="shared" ref="BY16:BY21" si="27">+BU16*5%</f>
+        <f t="shared" si="23"/>
         <v>2000000</v>
       </c>
       <c r="BZ16" s="348">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>42000000</v>
       </c>
       <c r="CA16" s="348" t="s">
@@ -17150,7 +17151,7 @@
         <v>0</v>
       </c>
       <c r="AN17" s="354">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>126923.07692307694</v>
       </c>
       <c r="AO17" s="354">
@@ -17194,21 +17195,21 @@
         <v>78200</v>
       </c>
       <c r="BF17" s="356">
+        <f t="shared" si="26"/>
+        <v>4292307.692307692</v>
+      </c>
+      <c r="BG17" s="356">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BG17" s="356">
-        <f t="shared" si="20"/>
-        <v>28615384.615384616</v>
+        <v>24323076.923076924</v>
       </c>
       <c r="BH17" s="356"/>
       <c r="BI17" s="356">
+        <f t="shared" si="20"/>
+        <v>12470476.923076924</v>
+      </c>
+      <c r="BJ17" s="348">
         <f t="shared" si="21"/>
-        <v>16762784.615384616</v>
-      </c>
-      <c r="BJ17" s="348">
-        <f t="shared" si="22"/>
-        <v>1764418</v>
+        <v>1120572</v>
       </c>
       <c r="BK17" s="356"/>
       <c r="BL17" s="356"/>
@@ -17221,11 +17222,11 @@
       <c r="BQ17" s="356"/>
       <c r="BR17" s="356"/>
       <c r="BS17" s="356" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>80%</v>
       </c>
       <c r="BT17" s="356">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>22892307.692307696</v>
       </c>
       <c r="BU17" s="347">
@@ -17239,11 +17240,11 @@
       </c>
       <c r="BX17" s="348"/>
       <c r="BY17" s="348">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>2000000</v>
       </c>
       <c r="BZ17" s="348">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>42000000</v>
       </c>
       <c r="CA17" s="348" t="s">
@@ -17377,7 +17378,7 @@
         <v>0</v>
       </c>
       <c r="AN18" s="354">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AO18" s="354">
@@ -17421,21 +17422,21 @@
         <v>69900</v>
       </c>
       <c r="BF18" s="356">
+        <f t="shared" si="26"/>
+        <v>1912557.6923076923</v>
+      </c>
+      <c r="BG18" s="356">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BG18" s="356">
-        <f t="shared" si="20"/>
-        <v>12750384.615384616</v>
+        <v>10837826.923076924</v>
       </c>
       <c r="BH18" s="356"/>
       <c r="BI18" s="356">
+        <f t="shared" si="20"/>
+        <v>-896123.07692307606</v>
+      </c>
+      <c r="BJ18" s="348">
         <f t="shared" si="21"/>
-        <v>1016434.615384616</v>
-      </c>
-      <c r="BJ18" s="348">
-        <f t="shared" si="22"/>
-        <v>50822</v>
+        <v>0</v>
       </c>
       <c r="BK18" s="356"/>
       <c r="BL18" s="356"/>
@@ -17448,11 +17449,11 @@
       <c r="BQ18" s="356"/>
       <c r="BR18" s="356"/>
       <c r="BS18" s="356" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>80%</v>
       </c>
       <c r="BT18" s="356">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>10200307.692307694</v>
       </c>
       <c r="BU18" s="347">
@@ -17466,11 +17467,11 @@
       </c>
       <c r="BX18" s="348"/>
       <c r="BY18" s="348">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>1150000</v>
       </c>
       <c r="BZ18" s="348">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>24150000</v>
       </c>
       <c r="CA18" s="348" t="s">
@@ -17602,7 +17603,7 @@
         <v>0</v>
       </c>
       <c r="AN19" s="354">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>126923.07692307694</v>
       </c>
       <c r="AO19" s="354">
@@ -17646,20 +17647,20 @@
         <v>48500</v>
       </c>
       <c r="BF19" s="356">
+        <f t="shared" si="26"/>
+        <v>1124711.5384615383</v>
+      </c>
+      <c r="BG19" s="356">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BG19" s="356">
-        <f t="shared" si="20"/>
-        <v>7498076.9230769221</v>
+        <v>6373365.384615384</v>
       </c>
       <c r="BH19" s="356"/>
       <c r="BI19" s="356">
+        <f t="shared" si="20"/>
+        <v>-5167384.615384616</v>
+      </c>
+      <c r="BJ19" s="348">
         <f t="shared" si="21"/>
-        <v>-4042673.0769230779</v>
-      </c>
-      <c r="BJ19" s="348">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BK19" s="356"/>
@@ -17673,11 +17674,11 @@
       <c r="BQ19" s="356"/>
       <c r="BR19" s="356"/>
       <c r="BS19" s="356" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>100%</v>
       </c>
       <c r="BT19" s="356">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>7498076.9230769221</v>
       </c>
       <c r="BU19" s="347">
@@ -17691,11 +17692,11 @@
       </c>
       <c r="BX19" s="348"/>
       <c r="BY19" s="348">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>550000</v>
       </c>
       <c r="BZ19" s="348">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>11550000</v>
       </c>
       <c r="CA19" s="348" t="s">
@@ -17829,7 +17830,7 @@
         <v>0</v>
       </c>
       <c r="AN20" s="354">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AO20" s="354">
@@ -17873,21 +17874,21 @@
         <v>63400</v>
       </c>
       <c r="BF20" s="356">
+        <f t="shared" si="26"/>
+        <v>1911620.1923076923</v>
+      </c>
+      <c r="BG20" s="356">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BG20" s="356">
-        <f t="shared" si="20"/>
-        <v>12744134.615384616</v>
+        <v>10832514.423076924</v>
       </c>
       <c r="BH20" s="356"/>
       <c r="BI20" s="356">
+        <f t="shared" si="20"/>
+        <v>-833185.57692307606</v>
+      </c>
+      <c r="BJ20" s="348">
         <f t="shared" si="21"/>
-        <v>1078434.615384616</v>
-      </c>
-      <c r="BJ20" s="348">
-        <f t="shared" si="22"/>
-        <v>53922</v>
+        <v>0</v>
       </c>
       <c r="BK20" s="356"/>
       <c r="BL20" s="356"/>
@@ -17900,11 +17901,11 @@
       <c r="BQ20" s="356"/>
       <c r="BR20" s="356"/>
       <c r="BS20" s="356" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>80%</v>
       </c>
       <c r="BT20" s="356">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>10195307.692307694</v>
       </c>
       <c r="BU20" s="347">
@@ -17918,11 +17919,11 @@
       </c>
       <c r="BX20" s="348"/>
       <c r="BY20" s="348">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>1150000</v>
       </c>
       <c r="BZ20" s="348">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>24150000</v>
       </c>
       <c r="CA20" s="348" t="s">
@@ -18054,7 +18055,7 @@
         <v>0</v>
       </c>
       <c r="AN21" s="354">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>126923.07692307694</v>
       </c>
       <c r="AO21" s="354">
@@ -18098,21 +18099,21 @@
         <v>63400</v>
       </c>
       <c r="BF21" s="356">
+        <f t="shared" si="26"/>
+        <v>1870846.1538461538</v>
+      </c>
+      <c r="BG21" s="356">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BG21" s="356">
-        <f t="shared" si="20"/>
-        <v>12472307.692307692</v>
+        <v>10601461.538461538</v>
       </c>
       <c r="BH21" s="356"/>
       <c r="BI21" s="356">
+        <f t="shared" si="20"/>
+        <v>-1095738.461538462</v>
+      </c>
+      <c r="BJ21" s="348">
         <f t="shared" si="21"/>
-        <v>775107.69230769202</v>
-      </c>
-      <c r="BJ21" s="348">
-        <f t="shared" si="22"/>
-        <v>38755</v>
+        <v>0</v>
       </c>
       <c r="BK21" s="356"/>
       <c r="BL21" s="356"/>
@@ -18125,11 +18126,11 @@
       <c r="BQ21" s="356"/>
       <c r="BR21" s="356"/>
       <c r="BS21" s="356" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>80%</v>
       </c>
       <c r="BT21" s="356">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>9977846.153846154</v>
       </c>
       <c r="BU21" s="347">
@@ -18143,11 +18144,11 @@
       </c>
       <c r="BX21" s="348"/>
       <c r="BY21" s="348">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>850000</v>
       </c>
       <c r="BZ21" s="348">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>17850000</v>
       </c>
       <c r="CA21" s="348" t="s">
